--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\jdbc\finance\acct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C0FC24-657B-498B-BA4B-03B5D3CBC3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CBE74C-0C24-4FA1-9CC3-24A8184314A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="4" activeTab="5" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="1455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="1456">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -4855,6 +4855,10 @@
   </si>
   <si>
     <t>广州仓库0001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>天津市河东区富民路05单位号</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -15707,7 +15711,7 @@
         <v>1451</v>
       </c>
       <c r="C3" t="s">
-        <v>1446</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">

--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\jdbc\finance\acct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA30A33C-9864-4D04-B9DC-0F9AAEF7EE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BE7CCB-8DA9-4C39-B6C7-0CDC63C2030A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="6" activeTab="10" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
   </bookViews>
@@ -1599,10 +1599,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>t_sales_order</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>t_billof_product</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4871,6 +4867,10 @@
   </si>
   <si>
     <t>receipt_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>t_order</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5358,7 +5358,7 @@
         <v>33</v>
       </c>
       <c r="F1" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G1" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -5413,7 +5413,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -5466,7 +5466,7 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>391</v>
+        <v>1458</v>
       </c>
       <c r="D2" t="s">
         <v>21</v>
@@ -5486,7 +5486,7 @@
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>391</v>
+        <v>1458</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
@@ -5506,7 +5506,7 @@
         <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>391</v>
+        <v>1458</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
@@ -5526,7 +5526,7 @@
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>391</v>
+        <v>1458</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
@@ -5546,7 +5546,7 @@
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D6" t="s">
         <v>21</v>
@@ -5566,7 +5566,7 @@
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D7" t="s">
         <v>21</v>
@@ -5586,7 +5586,7 @@
         <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
@@ -5606,7 +5606,7 @@
         <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -9120,10 +9120,10 @@
         <v>43</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -9131,10 +9131,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>429</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -9142,10 +9142,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>431</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -9153,10 +9153,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>433</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -9164,10 +9164,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -9175,10 +9175,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -9186,10 +9186,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -9197,10 +9197,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -9208,10 +9208,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -9219,10 +9219,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -9230,10 +9230,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>447</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -9241,10 +9241,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -9252,10 +9252,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>451</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -9263,10 +9263,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -9274,10 +9274,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>455</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -9285,10 +9285,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>457</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -9296,10 +9296,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>459</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -9307,10 +9307,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>461</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -9318,10 +9318,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>463</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -9329,10 +9329,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>465</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -9340,10 +9340,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>467</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -9351,10 +9351,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -9362,10 +9362,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -9373,10 +9373,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>473</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -9384,10 +9384,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -9395,10 +9395,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>477</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -9406,10 +9406,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>479</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -9417,10 +9417,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>481</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -9428,10 +9428,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -9439,10 +9439,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>485</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -9450,10 +9450,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>487</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -9461,10 +9461,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -9472,10 +9472,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>491</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -9483,10 +9483,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>493</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -9494,10 +9494,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>495</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -9505,10 +9505,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>497</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -9516,10 +9516,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>499</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -9527,10 +9527,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>501</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -9538,10 +9538,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>503</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -9549,10 +9549,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>505</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -9560,10 +9560,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>507</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -9571,10 +9571,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -9582,10 +9582,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>511</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -9593,10 +9593,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>513</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -9604,10 +9604,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -9615,10 +9615,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>517</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -9626,10 +9626,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>519</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -9637,10 +9637,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>521</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -9648,10 +9648,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>523</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -9659,10 +9659,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>525</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -9670,10 +9670,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>527</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -9681,10 +9681,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>529</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -9692,10 +9692,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>531</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -9703,10 +9703,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>533</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -9714,10 +9714,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>535</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -9725,10 +9725,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>537</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -9736,10 +9736,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>539</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -9747,10 +9747,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="C58" s="4" t="s">
         <v>541</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -9758,10 +9758,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>543</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -9769,10 +9769,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>545</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -9780,10 +9780,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>547</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -9791,10 +9791,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>549</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -9802,10 +9802,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>551</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -9813,10 +9813,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>553</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -9824,10 +9824,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>555</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -9835,10 +9835,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="C66" s="4" t="s">
         <v>557</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -9846,10 +9846,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="C67" s="4" t="s">
         <v>559</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -9857,10 +9857,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>561</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -9868,10 +9868,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>563</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -9879,10 +9879,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>565</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -9890,10 +9890,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>567</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -9901,10 +9901,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>569</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -9912,10 +9912,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>571</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -9923,10 +9923,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>573</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -9934,10 +9934,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="C75" s="4" t="s">
         <v>575</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -9945,10 +9945,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="C76" s="4" t="s">
         <v>577</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -9956,10 +9956,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>579</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -9967,10 +9967,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="C78" s="4" t="s">
         <v>581</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
@@ -9978,10 +9978,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>583</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
@@ -9989,10 +9989,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>585</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -10000,10 +10000,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>587</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
@@ -10011,10 +10011,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>589</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
@@ -10022,10 +10022,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>591</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -10033,10 +10033,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>593</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
@@ -10044,10 +10044,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>595</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
@@ -10055,10 +10055,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>597</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -10066,10 +10066,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>599</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -10077,10 +10077,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>601</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
@@ -10088,10 +10088,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>603</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
@@ -10099,10 +10099,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>605</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
@@ -10110,10 +10110,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="C91" s="4" t="s">
         <v>607</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
@@ -10121,10 +10121,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>609</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
@@ -10132,10 +10132,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="C93" s="4" t="s">
         <v>611</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
@@ -10143,10 +10143,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>613</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
@@ -10154,10 +10154,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>615</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
@@ -10165,10 +10165,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>617</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
@@ -10176,10 +10176,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>619</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
@@ -10187,10 +10187,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>621</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
@@ -10198,10 +10198,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="C99" s="4" t="s">
         <v>623</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
@@ -10209,10 +10209,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="C100" s="4" t="s">
         <v>625</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
@@ -10220,10 +10220,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="C101" s="4" t="s">
         <v>627</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
@@ -10231,10 +10231,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="C102" s="4" t="s">
         <v>629</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
@@ -10242,10 +10242,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="C103" s="4" t="s">
         <v>631</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
@@ -10253,10 +10253,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="C104" s="4" t="s">
         <v>633</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
@@ -10264,10 +10264,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="C105" s="4" t="s">
         <v>635</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
@@ -10275,10 +10275,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="C106" s="4" t="s">
         <v>637</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
@@ -10286,10 +10286,10 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="C107" s="4" t="s">
         <v>639</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
@@ -10297,10 +10297,10 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="C108" s="4" t="s">
         <v>641</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
@@ -10308,10 +10308,10 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="C109" s="4" t="s">
         <v>643</v>
-      </c>
-      <c r="C109" s="4" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -10319,10 +10319,10 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="C110" s="4" t="s">
         <v>645</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
@@ -10330,10 +10330,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C111" s="4" t="s">
         <v>647</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
@@ -10341,10 +10341,10 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="C112" s="4" t="s">
         <v>649</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
@@ -10352,10 +10352,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="C113" s="4" t="s">
         <v>651</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
@@ -10363,10 +10363,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C114" s="4" t="s">
         <v>653</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
@@ -10374,10 +10374,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="C115" s="4" t="s">
         <v>655</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
@@ -10385,10 +10385,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="C116" s="4" t="s">
         <v>657</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
@@ -10396,10 +10396,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="C117" s="4" t="s">
         <v>659</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
@@ -10407,10 +10407,10 @@
         <v>117</v>
       </c>
       <c r="B118" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="C118" s="4" t="s">
         <v>661</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
@@ -10418,10 +10418,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="C119" s="4" t="s">
         <v>663</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
@@ -10429,10 +10429,10 @@
         <v>119</v>
       </c>
       <c r="B120" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="C120" s="4" t="s">
         <v>665</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -10440,10 +10440,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="C121" s="4" t="s">
         <v>667</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
@@ -10451,10 +10451,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C122" s="4" t="s">
         <v>669</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
@@ -10462,10 +10462,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="C123" s="4" t="s">
         <v>671</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
@@ -10473,10 +10473,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="C124" s="4" t="s">
         <v>673</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
@@ -10484,10 +10484,10 @@
         <v>124</v>
       </c>
       <c r="B125" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="C125" s="4" t="s">
         <v>675</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
@@ -10495,10 +10495,10 @@
         <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="C126" s="4" t="s">
         <v>677</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
@@ -10506,10 +10506,10 @@
         <v>126</v>
       </c>
       <c r="B127" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="C127" s="4" t="s">
         <v>679</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
@@ -10517,10 +10517,10 @@
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="C128" s="4" t="s">
         <v>681</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
@@ -10528,10 +10528,10 @@
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="C129" s="4" t="s">
         <v>683</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
@@ -10539,10 +10539,10 @@
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="C130" s="4" t="s">
         <v>685</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
@@ -10550,10 +10550,10 @@
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C131" s="4" t="s">
         <v>687</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -10561,10 +10561,10 @@
         <v>131</v>
       </c>
       <c r="B132" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="C132" s="4" t="s">
         <v>689</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
@@ -10572,10 +10572,10 @@
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="C133" s="4" t="s">
         <v>691</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
@@ -10583,10 +10583,10 @@
         <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="C134" s="4" t="s">
         <v>693</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
@@ -10594,10 +10594,10 @@
         <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="C135" s="4" t="s">
         <v>695</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
@@ -10605,10 +10605,10 @@
         <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="C136" s="4" t="s">
         <v>697</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
@@ -10616,10 +10616,10 @@
         <v>136</v>
       </c>
       <c r="B137" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="C137" s="4" t="s">
         <v>699</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
@@ -10627,10 +10627,10 @@
         <v>137</v>
       </c>
       <c r="B138" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="C138" s="4" t="s">
         <v>701</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
@@ -10638,10 +10638,10 @@
         <v>138</v>
       </c>
       <c r="B139" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="C139" s="4" t="s">
         <v>703</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
@@ -10649,10 +10649,10 @@
         <v>139</v>
       </c>
       <c r="B140" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="C140" s="4" t="s">
         <v>705</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
@@ -10660,10 +10660,10 @@
         <v>140</v>
       </c>
       <c r="B141" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="C141" s="4" t="s">
         <v>707</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
@@ -10671,10 +10671,10 @@
         <v>141</v>
       </c>
       <c r="B142" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="C142" s="4" t="s">
         <v>709</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -10682,10 +10682,10 @@
         <v>142</v>
       </c>
       <c r="B143" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="C143" s="4" t="s">
         <v>711</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
@@ -10693,10 +10693,10 @@
         <v>143</v>
       </c>
       <c r="B144" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="C144" s="4" t="s">
         <v>713</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
@@ -10704,10 +10704,10 @@
         <v>144</v>
       </c>
       <c r="B145" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="C145" s="4" t="s">
         <v>715</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
@@ -10715,10 +10715,10 @@
         <v>145</v>
       </c>
       <c r="B146" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="C146" s="4" t="s">
         <v>717</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
@@ -10726,10 +10726,10 @@
         <v>146</v>
       </c>
       <c r="B147" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="C147" s="4" t="s">
         <v>719</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
@@ -10737,10 +10737,10 @@
         <v>147</v>
       </c>
       <c r="B148" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="C148" s="4" t="s">
         <v>721</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
@@ -10748,10 +10748,10 @@
         <v>148</v>
       </c>
       <c r="B149" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C149" s="4" t="s">
         <v>723</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
@@ -10759,10 +10759,10 @@
         <v>149</v>
       </c>
       <c r="B150" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="C150" s="4" t="s">
         <v>725</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
@@ -10770,10 +10770,10 @@
         <v>150</v>
       </c>
       <c r="B151" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="C151" s="4" t="s">
         <v>727</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
@@ -10781,10 +10781,10 @@
         <v>151</v>
       </c>
       <c r="B152" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="C152" s="4" t="s">
         <v>729</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
@@ -10792,10 +10792,10 @@
         <v>152</v>
       </c>
       <c r="B153" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="C153" s="4" t="s">
         <v>731</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -10803,10 +10803,10 @@
         <v>153</v>
       </c>
       <c r="B154" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="C154" s="4" t="s">
         <v>733</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
@@ -10814,10 +10814,10 @@
         <v>154</v>
       </c>
       <c r="B155" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="C155" s="4" t="s">
         <v>735</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
@@ -10825,10 +10825,10 @@
         <v>155</v>
       </c>
       <c r="B156" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="C156" s="4" t="s">
         <v>737</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
@@ -10836,10 +10836,10 @@
         <v>156</v>
       </c>
       <c r="B157" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="C157" s="4" t="s">
         <v>739</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
@@ -10847,10 +10847,10 @@
         <v>157</v>
       </c>
       <c r="B158" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="C158" s="4" t="s">
         <v>741</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
@@ -10858,10 +10858,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="C159" s="4" t="s">
         <v>743</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
@@ -10869,10 +10869,10 @@
         <v>159</v>
       </c>
       <c r="B160" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="C160" s="4" t="s">
         <v>745</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
@@ -10880,10 +10880,10 @@
         <v>160</v>
       </c>
       <c r="B161" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="C161" s="4" t="s">
         <v>747</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
@@ -10891,10 +10891,10 @@
         <v>161</v>
       </c>
       <c r="B162" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="C162" s="4" t="s">
         <v>749</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
@@ -10902,10 +10902,10 @@
         <v>162</v>
       </c>
       <c r="B163" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="C163" s="4" t="s">
         <v>751</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
@@ -10913,10 +10913,10 @@
         <v>163</v>
       </c>
       <c r="B164" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="C164" s="4" t="s">
         <v>753</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
@@ -10924,10 +10924,10 @@
         <v>164</v>
       </c>
       <c r="B165" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>755</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
@@ -10935,10 +10935,10 @@
         <v>165</v>
       </c>
       <c r="B166" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>757</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
@@ -10946,10 +10946,10 @@
         <v>166</v>
       </c>
       <c r="B167" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="C167" s="4" t="s">
         <v>759</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
@@ -10957,10 +10957,10 @@
         <v>167</v>
       </c>
       <c r="B168" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="C168" s="4" t="s">
         <v>761</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
@@ -10968,10 +10968,10 @@
         <v>168</v>
       </c>
       <c r="B169" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="C169" s="4" t="s">
         <v>763</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
@@ -10979,10 +10979,10 @@
         <v>169</v>
       </c>
       <c r="B170" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="C170" s="4" t="s">
         <v>765</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
@@ -10990,10 +10990,10 @@
         <v>170</v>
       </c>
       <c r="B171" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="C171" s="4" t="s">
         <v>767</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
@@ -11001,10 +11001,10 @@
         <v>171</v>
       </c>
       <c r="B172" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="C172" s="4" t="s">
         <v>769</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
@@ -11012,10 +11012,10 @@
         <v>172</v>
       </c>
       <c r="B173" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="C173" s="4" t="s">
         <v>771</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
@@ -11023,10 +11023,10 @@
         <v>173</v>
       </c>
       <c r="B174" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C174" s="4" t="s">
         <v>773</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
@@ -11034,10 +11034,10 @@
         <v>174</v>
       </c>
       <c r="B175" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="C175" s="4" t="s">
         <v>775</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
@@ -11045,10 +11045,10 @@
         <v>175</v>
       </c>
       <c r="B176" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="C176" s="4" t="s">
         <v>777</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
@@ -11056,10 +11056,10 @@
         <v>176</v>
       </c>
       <c r="B177" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="C177" s="4" t="s">
         <v>779</v>
-      </c>
-      <c r="C177" s="4" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
@@ -11067,10 +11067,10 @@
         <v>177</v>
       </c>
       <c r="B178" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="C178" s="4" t="s">
         <v>781</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
@@ -11078,10 +11078,10 @@
         <v>178</v>
       </c>
       <c r="B179" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="C179" s="4" t="s">
         <v>783</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
@@ -11089,10 +11089,10 @@
         <v>179</v>
       </c>
       <c r="B180" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="C180" s="4" t="s">
         <v>785</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
@@ -11100,10 +11100,10 @@
         <v>180</v>
       </c>
       <c r="B181" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="C181" s="4" t="s">
         <v>787</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
@@ -11111,10 +11111,10 @@
         <v>181</v>
       </c>
       <c r="B182" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="C182" s="4" t="s">
         <v>789</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
@@ -11122,10 +11122,10 @@
         <v>182</v>
       </c>
       <c r="B183" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C183" s="4" t="s">
         <v>791</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
@@ -11133,10 +11133,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="C184" s="4" t="s">
         <v>793</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
@@ -11144,10 +11144,10 @@
         <v>184</v>
       </c>
       <c r="B185" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="C185" s="4" t="s">
         <v>795</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
@@ -11155,10 +11155,10 @@
         <v>185</v>
       </c>
       <c r="B186" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="C186" s="4" t="s">
         <v>797</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
@@ -11166,10 +11166,10 @@
         <v>186</v>
       </c>
       <c r="B187" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="C187" s="4" t="s">
         <v>799</v>
-      </c>
-      <c r="C187" s="4" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
@@ -11177,10 +11177,10 @@
         <v>187</v>
       </c>
       <c r="B188" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="C188" s="4" t="s">
         <v>801</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
@@ -11188,10 +11188,10 @@
         <v>188</v>
       </c>
       <c r="B189" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="C189" s="4" t="s">
         <v>803</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
@@ -11199,10 +11199,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="C190" s="4" t="s">
         <v>805</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
@@ -11210,10 +11210,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="C191" s="4" t="s">
         <v>807</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
@@ -11221,10 +11221,10 @@
         <v>191</v>
       </c>
       <c r="B192" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="C192" s="4" t="s">
         <v>809</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.2">
@@ -11232,10 +11232,10 @@
         <v>192</v>
       </c>
       <c r="B193" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="C193" s="4" t="s">
         <v>811</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.2">
@@ -11243,10 +11243,10 @@
         <v>193</v>
       </c>
       <c r="B194" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="C194" s="4" t="s">
         <v>813</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.2">
@@ -11254,10 +11254,10 @@
         <v>194</v>
       </c>
       <c r="B195" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="C195" s="4" t="s">
         <v>815</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
@@ -11265,10 +11265,10 @@
         <v>195</v>
       </c>
       <c r="B196" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="C196" s="4" t="s">
         <v>817</v>
-      </c>
-      <c r="C196" s="4" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
@@ -11276,10 +11276,10 @@
         <v>196</v>
       </c>
       <c r="B197" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="C197" s="4" t="s">
         <v>819</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
@@ -11287,10 +11287,10 @@
         <v>197</v>
       </c>
       <c r="B198" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="C198" s="4" t="s">
         <v>821</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
@@ -11298,10 +11298,10 @@
         <v>198</v>
       </c>
       <c r="B199" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="C199" s="4" t="s">
         <v>823</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
@@ -11309,10 +11309,10 @@
         <v>199</v>
       </c>
       <c r="B200" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="C200" s="4" t="s">
         <v>825</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
@@ -11320,10 +11320,10 @@
         <v>200</v>
       </c>
       <c r="B201" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="C201" s="4" t="s">
         <v>827</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
@@ -11331,10 +11331,10 @@
         <v>201</v>
       </c>
       <c r="B202" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="C202" s="4" t="s">
         <v>829</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.2">
@@ -11342,10 +11342,10 @@
         <v>202</v>
       </c>
       <c r="B203" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="C203" s="4" t="s">
         <v>831</v>
-      </c>
-      <c r="C203" s="4" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.2">
@@ -11353,10 +11353,10 @@
         <v>203</v>
       </c>
       <c r="B204" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="C204" s="4" t="s">
         <v>833</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
@@ -11364,10 +11364,10 @@
         <v>204</v>
       </c>
       <c r="B205" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="C205" s="4" t="s">
         <v>835</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
@@ -11375,10 +11375,10 @@
         <v>205</v>
       </c>
       <c r="B206" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="C206" s="4" t="s">
         <v>837</v>
-      </c>
-      <c r="C206" s="4" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
@@ -11386,10 +11386,10 @@
         <v>206</v>
       </c>
       <c r="B207" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="C207" s="4" t="s">
         <v>839</v>
-      </c>
-      <c r="C207" s="4" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
@@ -11397,10 +11397,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="C208" s="4" t="s">
         <v>841</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -11408,10 +11408,10 @@
         <v>208</v>
       </c>
       <c r="B209" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="C209" s="4" t="s">
         <v>843</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
@@ -11419,10 +11419,10 @@
         <v>209</v>
       </c>
       <c r="B210" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="C210" s="4" t="s">
         <v>845</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
@@ -11430,10 +11430,10 @@
         <v>210</v>
       </c>
       <c r="B211" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="C211" s="4" t="s">
         <v>847</v>
-      </c>
-      <c r="C211" s="4" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
@@ -11441,10 +11441,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="C212" s="4" t="s">
         <v>849</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
@@ -11452,10 +11452,10 @@
         <v>212</v>
       </c>
       <c r="B213" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="C213" s="4" t="s">
         <v>851</v>
-      </c>
-      <c r="C213" s="4" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
@@ -11463,10 +11463,10 @@
         <v>213</v>
       </c>
       <c r="B214" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="C214" s="4" t="s">
         <v>853</v>
-      </c>
-      <c r="C214" s="4" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
@@ -11474,10 +11474,10 @@
         <v>214</v>
       </c>
       <c r="B215" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="C215" s="4" t="s">
         <v>855</v>
-      </c>
-      <c r="C215" s="4" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
@@ -11485,10 +11485,10 @@
         <v>215</v>
       </c>
       <c r="B216" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="C216" s="4" t="s">
         <v>857</v>
-      </c>
-      <c r="C216" s="4" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
@@ -11496,10 +11496,10 @@
         <v>216</v>
       </c>
       <c r="B217" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="C217" s="4" t="s">
         <v>859</v>
-      </c>
-      <c r="C217" s="4" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
@@ -11507,10 +11507,10 @@
         <v>217</v>
       </c>
       <c r="B218" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="C218" s="4" t="s">
         <v>861</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
@@ -11518,10 +11518,10 @@
         <v>218</v>
       </c>
       <c r="B219" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="C219" s="4" t="s">
         <v>863</v>
-      </c>
-      <c r="C219" s="4" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -11529,10 +11529,10 @@
         <v>219</v>
       </c>
       <c r="B220" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="C220" s="4" t="s">
         <v>865</v>
-      </c>
-      <c r="C220" s="4" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
@@ -11540,10 +11540,10 @@
         <v>220</v>
       </c>
       <c r="B221" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="C221" s="4" t="s">
         <v>867</v>
-      </c>
-      <c r="C221" s="4" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
@@ -11551,10 +11551,10 @@
         <v>221</v>
       </c>
       <c r="B222" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="C222" s="4" t="s">
         <v>869</v>
-      </c>
-      <c r="C222" s="4" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
@@ -11562,10 +11562,10 @@
         <v>222</v>
       </c>
       <c r="B223" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="C223" s="4" t="s">
         <v>871</v>
-      </c>
-      <c r="C223" s="4" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.2">
@@ -11573,10 +11573,10 @@
         <v>223</v>
       </c>
       <c r="B224" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="C224" s="4" t="s">
         <v>873</v>
-      </c>
-      <c r="C224" s="4" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
@@ -11584,10 +11584,10 @@
         <v>224</v>
       </c>
       <c r="B225" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="C225" s="4" t="s">
         <v>875</v>
-      </c>
-      <c r="C225" s="4" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
@@ -11595,10 +11595,10 @@
         <v>225</v>
       </c>
       <c r="B226" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="C226" s="4" t="s">
         <v>877</v>
-      </c>
-      <c r="C226" s="4" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.2">
@@ -11606,10 +11606,10 @@
         <v>226</v>
       </c>
       <c r="B227" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="C227" s="4" t="s">
         <v>879</v>
-      </c>
-      <c r="C227" s="4" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.2">
@@ -11617,10 +11617,10 @@
         <v>227</v>
       </c>
       <c r="B228" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="C228" s="4" t="s">
         <v>881</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.2">
@@ -11628,10 +11628,10 @@
         <v>228</v>
       </c>
       <c r="B229" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="C229" s="4" t="s">
         <v>883</v>
-      </c>
-      <c r="C229" s="4" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
@@ -11639,10 +11639,10 @@
         <v>229</v>
       </c>
       <c r="B230" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="C230" s="4" t="s">
         <v>885</v>
-      </c>
-      <c r="C230" s="4" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -11650,10 +11650,10 @@
         <v>230</v>
       </c>
       <c r="B231" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="C231" s="4" t="s">
         <v>887</v>
-      </c>
-      <c r="C231" s="4" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
@@ -11661,10 +11661,10 @@
         <v>231</v>
       </c>
       <c r="B232" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="C232" s="4" t="s">
         <v>889</v>
-      </c>
-      <c r="C232" s="4" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
@@ -11672,10 +11672,10 @@
         <v>232</v>
       </c>
       <c r="B233" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="C233" s="4" t="s">
         <v>891</v>
-      </c>
-      <c r="C233" s="4" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.2">
@@ -11683,10 +11683,10 @@
         <v>233</v>
       </c>
       <c r="B234" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="C234" s="4" t="s">
         <v>893</v>
-      </c>
-      <c r="C234" s="4" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.2">
@@ -11694,10 +11694,10 @@
         <v>234</v>
       </c>
       <c r="B235" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="C235" s="4" t="s">
         <v>895</v>
-      </c>
-      <c r="C235" s="4" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.2">
@@ -11705,10 +11705,10 @@
         <v>235</v>
       </c>
       <c r="B236" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="C236" s="4" t="s">
         <v>897</v>
-      </c>
-      <c r="C236" s="4" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.2">
@@ -11716,10 +11716,10 @@
         <v>236</v>
       </c>
       <c r="B237" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="C237" s="4" t="s">
         <v>899</v>
-      </c>
-      <c r="C237" s="4" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.2">
@@ -11727,10 +11727,10 @@
         <v>237</v>
       </c>
       <c r="B238" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="C238" s="4" t="s">
         <v>901</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.2">
@@ -11738,10 +11738,10 @@
         <v>238</v>
       </c>
       <c r="B239" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="C239" s="4" t="s">
         <v>903</v>
-      </c>
-      <c r="C239" s="4" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.2">
@@ -11749,10 +11749,10 @@
         <v>239</v>
       </c>
       <c r="B240" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="C240" s="4" t="s">
         <v>905</v>
-      </c>
-      <c r="C240" s="4" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
@@ -11760,10 +11760,10 @@
         <v>240</v>
       </c>
       <c r="B241" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="C241" s="4" t="s">
         <v>907</v>
-      </c>
-      <c r="C241" s="4" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
@@ -11771,10 +11771,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="C242" s="4" t="s">
         <v>909</v>
-      </c>
-      <c r="C242" s="4" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.2">
@@ -11782,10 +11782,10 @@
         <v>242</v>
       </c>
       <c r="B243" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="C243" s="4" t="s">
         <v>911</v>
-      </c>
-      <c r="C243" s="4" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
@@ -11793,10 +11793,10 @@
         <v>243</v>
       </c>
       <c r="B244" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="C244" s="4" t="s">
         <v>913</v>
-      </c>
-      <c r="C244" s="4" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.2">
@@ -11804,10 +11804,10 @@
         <v>244</v>
       </c>
       <c r="B245" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="C245" s="4" t="s">
         <v>915</v>
-      </c>
-      <c r="C245" s="4" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.2">
@@ -11815,10 +11815,10 @@
         <v>245</v>
       </c>
       <c r="B246" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="C246" s="4" t="s">
         <v>917</v>
-      </c>
-      <c r="C246" s="4" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.2">
@@ -11826,10 +11826,10 @@
         <v>246</v>
       </c>
       <c r="B247" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="C247" s="4" t="s">
         <v>919</v>
-      </c>
-      <c r="C247" s="4" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.2">
@@ -11837,10 +11837,10 @@
         <v>247</v>
       </c>
       <c r="B248" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="C248" s="4" t="s">
         <v>921</v>
-      </c>
-      <c r="C248" s="4" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.2">
@@ -11848,10 +11848,10 @@
         <v>248</v>
       </c>
       <c r="B249" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C249" s="4" t="s">
         <v>923</v>
-      </c>
-      <c r="C249" s="4" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.2">
@@ -11859,10 +11859,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="C250" s="4" t="s">
         <v>925</v>
-      </c>
-      <c r="C250" s="4" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.2">
@@ -11870,10 +11870,10 @@
         <v>250</v>
       </c>
       <c r="B251" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="C251" s="4" t="s">
         <v>927</v>
-      </c>
-      <c r="C251" s="4" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
@@ -11881,10 +11881,10 @@
         <v>251</v>
       </c>
       <c r="B252" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="C252" s="4" t="s">
         <v>929</v>
-      </c>
-      <c r="C252" s="4" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
@@ -11892,10 +11892,10 @@
         <v>252</v>
       </c>
       <c r="B253" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C253" s="4" t="s">
         <v>931</v>
-      </c>
-      <c r="C253" s="4" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.2">
@@ -11903,10 +11903,10 @@
         <v>253</v>
       </c>
       <c r="B254" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="C254" s="4" t="s">
         <v>933</v>
-      </c>
-      <c r="C254" s="4" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
@@ -11914,10 +11914,10 @@
         <v>254</v>
       </c>
       <c r="B255" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="C255" s="4" t="s">
         <v>935</v>
-      </c>
-      <c r="C255" s="4" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.2">
@@ -11925,10 +11925,10 @@
         <v>255</v>
       </c>
       <c r="B256" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="C256" s="4" t="s">
         <v>937</v>
-      </c>
-      <c r="C256" s="4" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.2">
@@ -11936,10 +11936,10 @@
         <v>256</v>
       </c>
       <c r="B257" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="C257" s="4" t="s">
         <v>939</v>
-      </c>
-      <c r="C257" s="4" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.2">
@@ -11947,10 +11947,10 @@
         <v>257</v>
       </c>
       <c r="B258" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="C258" s="4" t="s">
         <v>941</v>
-      </c>
-      <c r="C258" s="4" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.2">
@@ -11958,10 +11958,10 @@
         <v>258</v>
       </c>
       <c r="B259" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="C259" s="4" t="s">
         <v>943</v>
-      </c>
-      <c r="C259" s="4" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.2">
@@ -11969,10 +11969,10 @@
         <v>259</v>
       </c>
       <c r="B260" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="C260" s="4" t="s">
         <v>945</v>
-      </c>
-      <c r="C260" s="4" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.2">
@@ -11980,10 +11980,10 @@
         <v>260</v>
       </c>
       <c r="B261" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="C261" s="4" t="s">
         <v>947</v>
-      </c>
-      <c r="C261" s="4" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.2">
@@ -11991,10 +11991,10 @@
         <v>261</v>
       </c>
       <c r="B262" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="C262" s="4" t="s">
         <v>949</v>
-      </c>
-      <c r="C262" s="4" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
@@ -12002,10 +12002,10 @@
         <v>262</v>
       </c>
       <c r="B263" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="C263" s="4" t="s">
         <v>951</v>
-      </c>
-      <c r="C263" s="4" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
@@ -12013,10 +12013,10 @@
         <v>263</v>
       </c>
       <c r="B264" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C264" s="4" t="s">
         <v>953</v>
-      </c>
-      <c r="C264" s="4" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
@@ -12024,10 +12024,10 @@
         <v>264</v>
       </c>
       <c r="B265" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="C265" s="4" t="s">
         <v>955</v>
-      </c>
-      <c r="C265" s="4" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
@@ -12035,10 +12035,10 @@
         <v>265</v>
       </c>
       <c r="B266" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="C266" s="4" t="s">
         <v>957</v>
-      </c>
-      <c r="C266" s="4" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.2">
@@ -12046,10 +12046,10 @@
         <v>266</v>
       </c>
       <c r="B267" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="C267" s="4" t="s">
         <v>959</v>
-      </c>
-      <c r="C267" s="4" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.2">
@@ -12057,10 +12057,10 @@
         <v>267</v>
       </c>
       <c r="B268" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="C268" s="4" t="s">
         <v>961</v>
-      </c>
-      <c r="C268" s="4" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.2">
@@ -12068,10 +12068,10 @@
         <v>268</v>
       </c>
       <c r="B269" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="C269" s="4" t="s">
         <v>963</v>
-      </c>
-      <c r="C269" s="4" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.2">
@@ -12079,10 +12079,10 @@
         <v>269</v>
       </c>
       <c r="B270" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="C270" s="4" t="s">
         <v>965</v>
-      </c>
-      <c r="C270" s="4" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.2">
@@ -12090,10 +12090,10 @@
         <v>270</v>
       </c>
       <c r="B271" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="C271" s="4" t="s">
         <v>967</v>
-      </c>
-      <c r="C271" s="4" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.2">
@@ -12101,10 +12101,10 @@
         <v>271</v>
       </c>
       <c r="B272" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="C272" s="4" t="s">
         <v>969</v>
-      </c>
-      <c r="C272" s="4" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.2">
@@ -12112,10 +12112,10 @@
         <v>272</v>
       </c>
       <c r="B273" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="C273" s="4" t="s">
         <v>971</v>
-      </c>
-      <c r="C273" s="4" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
@@ -12123,10 +12123,10 @@
         <v>273</v>
       </c>
       <c r="B274" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="C274" s="4" t="s">
         <v>973</v>
-      </c>
-      <c r="C274" s="4" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
@@ -12134,10 +12134,10 @@
         <v>274</v>
       </c>
       <c r="B275" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="C275" s="4" t="s">
         <v>975</v>
-      </c>
-      <c r="C275" s="4" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
@@ -12145,10 +12145,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="C276" s="4" t="s">
         <v>977</v>
-      </c>
-      <c r="C276" s="4" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
@@ -12156,10 +12156,10 @@
         <v>276</v>
       </c>
       <c r="B277" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="C277" s="4" t="s">
         <v>979</v>
-      </c>
-      <c r="C277" s="4" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.2">
@@ -12167,10 +12167,10 @@
         <v>277</v>
       </c>
       <c r="B278" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="C278" s="4" t="s">
         <v>981</v>
-      </c>
-      <c r="C278" s="4" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.2">
@@ -12178,10 +12178,10 @@
         <v>278</v>
       </c>
       <c r="B279" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="C279" s="4" t="s">
         <v>983</v>
-      </c>
-      <c r="C279" s="4" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.2">
@@ -12189,10 +12189,10 @@
         <v>279</v>
       </c>
       <c r="B280" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="C280" s="4" t="s">
         <v>985</v>
-      </c>
-      <c r="C280" s="4" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.2">
@@ -12200,10 +12200,10 @@
         <v>280</v>
       </c>
       <c r="B281" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="C281" s="4" t="s">
         <v>987</v>
-      </c>
-      <c r="C281" s="4" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
@@ -12211,10 +12211,10 @@
         <v>281</v>
       </c>
       <c r="B282" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="C282" s="4" t="s">
         <v>989</v>
-      </c>
-      <c r="C282" s="4" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.2">
@@ -12222,10 +12222,10 @@
         <v>282</v>
       </c>
       <c r="B283" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="C283" s="4" t="s">
         <v>991</v>
-      </c>
-      <c r="C283" s="4" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.2">
@@ -12233,10 +12233,10 @@
         <v>283</v>
       </c>
       <c r="B284" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="C284" s="4" t="s">
         <v>993</v>
-      </c>
-      <c r="C284" s="4" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
@@ -12244,10 +12244,10 @@
         <v>284</v>
       </c>
       <c r="B285" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="C285" s="4" t="s">
         <v>995</v>
-      </c>
-      <c r="C285" s="4" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
@@ -12255,10 +12255,10 @@
         <v>285</v>
       </c>
       <c r="B286" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="C286" s="4" t="s">
         <v>997</v>
-      </c>
-      <c r="C286" s="4" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
@@ -12266,10 +12266,10 @@
         <v>286</v>
       </c>
       <c r="B287" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="C287" s="4" t="s">
         <v>999</v>
-      </c>
-      <c r="C287" s="4" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
@@ -12277,10 +12277,10 @@
         <v>287</v>
       </c>
       <c r="B288" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C288" s="4" t="s">
         <v>1001</v>
-      </c>
-      <c r="C288" s="4" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.2">
@@ -12288,10 +12288,10 @@
         <v>288</v>
       </c>
       <c r="B289" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C289" s="4" t="s">
         <v>1003</v>
-      </c>
-      <c r="C289" s="4" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.2">
@@ -12299,10 +12299,10 @@
         <v>289</v>
       </c>
       <c r="B290" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C290" s="4" t="s">
         <v>1005</v>
-      </c>
-      <c r="C290" s="4" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.2">
@@ -12310,10 +12310,10 @@
         <v>290</v>
       </c>
       <c r="B291" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C291" s="4" t="s">
         <v>1007</v>
-      </c>
-      <c r="C291" s="4" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.2">
@@ -12321,10 +12321,10 @@
         <v>291</v>
       </c>
       <c r="B292" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C292" s="4" t="s">
         <v>1009</v>
-      </c>
-      <c r="C292" s="4" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.2">
@@ -12332,10 +12332,10 @@
         <v>292</v>
       </c>
       <c r="B293" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C293" s="4" t="s">
         <v>1011</v>
-      </c>
-      <c r="C293" s="4" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.2">
@@ -12343,10 +12343,10 @@
         <v>293</v>
       </c>
       <c r="B294" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C294" s="4" t="s">
         <v>1013</v>
-      </c>
-      <c r="C294" s="4" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.2">
@@ -12354,10 +12354,10 @@
         <v>294</v>
       </c>
       <c r="B295" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C295" s="4" t="s">
         <v>1015</v>
-      </c>
-      <c r="C295" s="4" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
@@ -12365,10 +12365,10 @@
         <v>295</v>
       </c>
       <c r="B296" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C296" s="4" t="s">
         <v>1017</v>
-      </c>
-      <c r="C296" s="4" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
@@ -12376,10 +12376,10 @@
         <v>296</v>
       </c>
       <c r="B297" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C297" s="4" t="s">
         <v>1019</v>
-      </c>
-      <c r="C297" s="4" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
@@ -12387,10 +12387,10 @@
         <v>297</v>
       </c>
       <c r="B298" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C298" s="4" t="s">
         <v>1021</v>
-      </c>
-      <c r="C298" s="4" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
@@ -12398,10 +12398,10 @@
         <v>298</v>
       </c>
       <c r="B299" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C299" s="4" t="s">
         <v>1023</v>
-      </c>
-      <c r="C299" s="4" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.2">
@@ -12409,10 +12409,10 @@
         <v>299</v>
       </c>
       <c r="B300" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C300" s="4" t="s">
         <v>1025</v>
-      </c>
-      <c r="C300" s="4" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.2">
@@ -12420,10 +12420,10 @@
         <v>300</v>
       </c>
       <c r="B301" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C301" s="4" t="s">
         <v>1027</v>
-      </c>
-      <c r="C301" s="4" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.2">
@@ -12431,10 +12431,10 @@
         <v>301</v>
       </c>
       <c r="B302" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C302" s="4" t="s">
         <v>1029</v>
-      </c>
-      <c r="C302" s="4" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.2">
@@ -12442,10 +12442,10 @@
         <v>302</v>
       </c>
       <c r="B303" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C303" s="4" t="s">
         <v>1031</v>
-      </c>
-      <c r="C303" s="4" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.2">
@@ -12453,10 +12453,10 @@
         <v>303</v>
       </c>
       <c r="B304" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C304" s="4" t="s">
         <v>1033</v>
-      </c>
-      <c r="C304" s="4" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.2">
@@ -12464,10 +12464,10 @@
         <v>304</v>
       </c>
       <c r="B305" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C305" s="4" t="s">
         <v>1035</v>
-      </c>
-      <c r="C305" s="4" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.2">
@@ -12475,10 +12475,10 @@
         <v>305</v>
       </c>
       <c r="B306" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C306" s="4" t="s">
         <v>1037</v>
-      </c>
-      <c r="C306" s="4" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
@@ -12486,10 +12486,10 @@
         <v>306</v>
       </c>
       <c r="B307" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C307" s="4" t="s">
         <v>1039</v>
-      </c>
-      <c r="C307" s="4" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
@@ -12497,10 +12497,10 @@
         <v>307</v>
       </c>
       <c r="B308" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C308" s="4" t="s">
         <v>1041</v>
-      </c>
-      <c r="C308" s="4" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.2">
@@ -12508,10 +12508,10 @@
         <v>308</v>
       </c>
       <c r="B309" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C309" s="4" t="s">
         <v>1043</v>
-      </c>
-      <c r="C309" s="4" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
@@ -12519,10 +12519,10 @@
         <v>309</v>
       </c>
       <c r="B310" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C310" s="4" t="s">
         <v>1045</v>
-      </c>
-      <c r="C310" s="4" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.2">
@@ -12530,10 +12530,10 @@
         <v>310</v>
       </c>
       <c r="B311" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C311" s="4" t="s">
         <v>1047</v>
-      </c>
-      <c r="C311" s="4" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.2">
@@ -12541,10 +12541,10 @@
         <v>311</v>
       </c>
       <c r="B312" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C312" s="4" t="s">
         <v>1049</v>
-      </c>
-      <c r="C312" s="4" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.2">
@@ -12552,10 +12552,10 @@
         <v>312</v>
       </c>
       <c r="B313" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C313" s="4" t="s">
         <v>1051</v>
-      </c>
-      <c r="C313" s="4" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.2">
@@ -12563,10 +12563,10 @@
         <v>313</v>
       </c>
       <c r="B314" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C314" s="4" t="s">
         <v>1053</v>
-      </c>
-      <c r="C314" s="4" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.2">
@@ -12574,10 +12574,10 @@
         <v>314</v>
       </c>
       <c r="B315" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C315" s="4" t="s">
         <v>1055</v>
-      </c>
-      <c r="C315" s="4" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.2">
@@ -12585,10 +12585,10 @@
         <v>315</v>
       </c>
       <c r="B316" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C316" s="4" t="s">
         <v>1057</v>
-      </c>
-      <c r="C316" s="4" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.2">
@@ -12596,10 +12596,10 @@
         <v>316</v>
       </c>
       <c r="B317" s="4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C317" s="4" t="s">
         <v>1059</v>
-      </c>
-      <c r="C317" s="4" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
@@ -12607,10 +12607,10 @@
         <v>317</v>
       </c>
       <c r="B318" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C318" s="4" t="s">
         <v>1061</v>
-      </c>
-      <c r="C318" s="4" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
@@ -12618,10 +12618,10 @@
         <v>318</v>
       </c>
       <c r="B319" s="4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C319" s="4" t="s">
         <v>1063</v>
-      </c>
-      <c r="C319" s="4" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.2">
@@ -12629,10 +12629,10 @@
         <v>319</v>
       </c>
       <c r="B320" s="4" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C320" s="4" t="s">
         <v>1065</v>
-      </c>
-      <c r="C320" s="4" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
@@ -12640,10 +12640,10 @@
         <v>320</v>
       </c>
       <c r="B321" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C321" s="4" t="s">
         <v>1067</v>
-      </c>
-      <c r="C321" s="4" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.2">
@@ -12651,10 +12651,10 @@
         <v>321</v>
       </c>
       <c r="B322" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C322" s="4" t="s">
         <v>1069</v>
-      </c>
-      <c r="C322" s="4" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.2">
@@ -12662,10 +12662,10 @@
         <v>322</v>
       </c>
       <c r="B323" s="4" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C323" s="4" t="s">
         <v>1071</v>
-      </c>
-      <c r="C323" s="4" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.2">
@@ -12673,10 +12673,10 @@
         <v>323</v>
       </c>
       <c r="B324" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C324" s="4" t="s">
         <v>1073</v>
-      </c>
-      <c r="C324" s="4" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.2">
@@ -12684,10 +12684,10 @@
         <v>324</v>
       </c>
       <c r="B325" s="4" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C325" s="4" t="s">
         <v>1075</v>
-      </c>
-      <c r="C325" s="4" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.2">
@@ -12695,10 +12695,10 @@
         <v>325</v>
       </c>
       <c r="B326" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C326" s="4" t="s">
         <v>1077</v>
-      </c>
-      <c r="C326" s="4" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.2">
@@ -12706,10 +12706,10 @@
         <v>326</v>
       </c>
       <c r="B327" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C327" s="4" t="s">
         <v>1079</v>
-      </c>
-      <c r="C327" s="4" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.2">
@@ -12717,10 +12717,10 @@
         <v>327</v>
       </c>
       <c r="B328" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C328" s="4" t="s">
         <v>1081</v>
-      </c>
-      <c r="C328" s="4" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
@@ -12728,10 +12728,10 @@
         <v>328</v>
       </c>
       <c r="B329" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C329" s="4" t="s">
         <v>1083</v>
-      </c>
-      <c r="C329" s="4" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
@@ -12739,10 +12739,10 @@
         <v>329</v>
       </c>
       <c r="B330" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C330" s="4" t="s">
         <v>1085</v>
-      </c>
-      <c r="C330" s="4" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
@@ -12750,10 +12750,10 @@
         <v>330</v>
       </c>
       <c r="B331" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C331" s="4" t="s">
         <v>1087</v>
-      </c>
-      <c r="C331" s="4" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
@@ -12761,10 +12761,10 @@
         <v>331</v>
       </c>
       <c r="B332" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C332" s="4" t="s">
         <v>1089</v>
-      </c>
-      <c r="C332" s="4" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.2">
@@ -12772,10 +12772,10 @@
         <v>332</v>
       </c>
       <c r="B333" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C333" s="4" t="s">
         <v>1091</v>
-      </c>
-      <c r="C333" s="4" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.2">
@@ -12783,10 +12783,10 @@
         <v>333</v>
       </c>
       <c r="B334" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C334" s="4" t="s">
         <v>1093</v>
-      </c>
-      <c r="C334" s="4" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.2">
@@ -12794,10 +12794,10 @@
         <v>334</v>
       </c>
       <c r="B335" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C335" s="4" t="s">
         <v>1095</v>
-      </c>
-      <c r="C335" s="4" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.2">
@@ -12805,10 +12805,10 @@
         <v>335</v>
       </c>
       <c r="B336" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C336" s="4" t="s">
         <v>1097</v>
-      </c>
-      <c r="C336" s="4" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.2">
@@ -12816,10 +12816,10 @@
         <v>336</v>
       </c>
       <c r="B337" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C337" s="4" t="s">
         <v>1099</v>
-      </c>
-      <c r="C337" s="4" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.2">
@@ -12827,10 +12827,10 @@
         <v>337</v>
       </c>
       <c r="B338" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C338" s="4" t="s">
         <v>1101</v>
-      </c>
-      <c r="C338" s="4" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.2">
@@ -12838,10 +12838,10 @@
         <v>338</v>
       </c>
       <c r="B339" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C339" s="4" t="s">
         <v>1103</v>
-      </c>
-      <c r="C339" s="4" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
@@ -12849,10 +12849,10 @@
         <v>339</v>
       </c>
       <c r="B340" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C340" s="4" t="s">
         <v>1105</v>
-      </c>
-      <c r="C340" s="4" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
@@ -12860,10 +12860,10 @@
         <v>340</v>
       </c>
       <c r="B341" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C341" s="4" t="s">
         <v>1107</v>
-      </c>
-      <c r="C341" s="4" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.2">
@@ -12871,10 +12871,10 @@
         <v>341</v>
       </c>
       <c r="B342" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C342" s="4" t="s">
         <v>1109</v>
-      </c>
-      <c r="C342" s="4" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
@@ -12882,10 +12882,10 @@
         <v>342</v>
       </c>
       <c r="B343" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C343" s="4" t="s">
         <v>1111</v>
-      </c>
-      <c r="C343" s="4" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.2">
@@ -12893,10 +12893,10 @@
         <v>343</v>
       </c>
       <c r="B344" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C344" s="4" t="s">
         <v>1113</v>
-      </c>
-      <c r="C344" s="4" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.2">
@@ -12904,10 +12904,10 @@
         <v>344</v>
       </c>
       <c r="B345" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C345" s="4" t="s">
         <v>1115</v>
-      </c>
-      <c r="C345" s="4" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.2">
@@ -12915,10 +12915,10 @@
         <v>345</v>
       </c>
       <c r="B346" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C346" s="4" t="s">
         <v>1117</v>
-      </c>
-      <c r="C346" s="4" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.2">
@@ -12926,10 +12926,10 @@
         <v>346</v>
       </c>
       <c r="B347" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C347" s="4" t="s">
         <v>1119</v>
-      </c>
-      <c r="C347" s="4" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.2">
@@ -12937,10 +12937,10 @@
         <v>347</v>
       </c>
       <c r="B348" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C348" s="4" t="s">
         <v>1121</v>
-      </c>
-      <c r="C348" s="4" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.2">
@@ -12948,10 +12948,10 @@
         <v>348</v>
       </c>
       <c r="B349" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C349" s="4" t="s">
         <v>1123</v>
-      </c>
-      <c r="C349" s="4" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.2">
@@ -12959,10 +12959,10 @@
         <v>349</v>
       </c>
       <c r="B350" s="4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C350" s="4" t="s">
         <v>1125</v>
-      </c>
-      <c r="C350" s="4" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
@@ -12970,10 +12970,10 @@
         <v>350</v>
       </c>
       <c r="B351" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C351" s="4" t="s">
         <v>1127</v>
-      </c>
-      <c r="C351" s="4" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
@@ -12981,10 +12981,10 @@
         <v>351</v>
       </c>
       <c r="B352" s="4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C352" s="4" t="s">
         <v>1129</v>
-      </c>
-      <c r="C352" s="4" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.2">
@@ -12992,10 +12992,10 @@
         <v>352</v>
       </c>
       <c r="B353" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C353" s="4" t="s">
         <v>1131</v>
-      </c>
-      <c r="C353" s="4" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
@@ -13003,10 +13003,10 @@
         <v>353</v>
       </c>
       <c r="B354" s="4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C354" s="4" t="s">
         <v>1133</v>
-      </c>
-      <c r="C354" s="4" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.2">
@@ -13014,10 +13014,10 @@
         <v>354</v>
       </c>
       <c r="B355" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C355" s="4" t="s">
         <v>1135</v>
-      </c>
-      <c r="C355" s="4" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.2">
@@ -13025,10 +13025,10 @@
         <v>355</v>
       </c>
       <c r="B356" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C356" s="4" t="s">
         <v>1137</v>
-      </c>
-      <c r="C356" s="4" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.2">
@@ -13036,10 +13036,10 @@
         <v>356</v>
       </c>
       <c r="B357" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C357" s="4" t="s">
         <v>1139</v>
-      </c>
-      <c r="C357" s="4" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.2">
@@ -13047,10 +13047,10 @@
         <v>357</v>
       </c>
       <c r="B358" s="4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C358" s="4" t="s">
         <v>1141</v>
-      </c>
-      <c r="C358" s="4" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.2">
@@ -13058,10 +13058,10 @@
         <v>358</v>
       </c>
       <c r="B359" s="4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C359" s="4" t="s">
         <v>1143</v>
-      </c>
-      <c r="C359" s="4" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.2">
@@ -13069,10 +13069,10 @@
         <v>359</v>
       </c>
       <c r="B360" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C360" s="4" t="s">
         <v>1145</v>
-      </c>
-      <c r="C360" s="4" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.2">
@@ -13080,10 +13080,10 @@
         <v>360</v>
       </c>
       <c r="B361" s="4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C361" s="4" t="s">
         <v>1147</v>
-      </c>
-      <c r="C361" s="4" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
@@ -13091,10 +13091,10 @@
         <v>361</v>
       </c>
       <c r="B362" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C362" s="4" t="s">
         <v>1149</v>
-      </c>
-      <c r="C362" s="4" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
@@ -13102,10 +13102,10 @@
         <v>362</v>
       </c>
       <c r="B363" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C363" s="4" t="s">
         <v>1151</v>
-      </c>
-      <c r="C363" s="4" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.2">
@@ -13113,10 +13113,10 @@
         <v>363</v>
       </c>
       <c r="B364" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C364" s="4" t="s">
         <v>1153</v>
-      </c>
-      <c r="C364" s="4" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
@@ -13124,10 +13124,10 @@
         <v>364</v>
       </c>
       <c r="B365" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C365" s="4" t="s">
         <v>1155</v>
-      </c>
-      <c r="C365" s="4" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.2">
@@ -13135,10 +13135,10 @@
         <v>365</v>
       </c>
       <c r="B366" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C366" s="4" t="s">
         <v>1157</v>
-      </c>
-      <c r="C366" s="4" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.2">
@@ -13146,10 +13146,10 @@
         <v>366</v>
       </c>
       <c r="B367" s="4" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C367" s="4" t="s">
         <v>1159</v>
-      </c>
-      <c r="C367" s="4" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.2">
@@ -13157,10 +13157,10 @@
         <v>367</v>
       </c>
       <c r="B368" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C368" s="4" t="s">
         <v>1161</v>
-      </c>
-      <c r="C368" s="4" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.2">
@@ -13168,10 +13168,10 @@
         <v>368</v>
       </c>
       <c r="B369" s="4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C369" s="4" t="s">
         <v>1163</v>
-      </c>
-      <c r="C369" s="4" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.2">
@@ -13179,10 +13179,10 @@
         <v>369</v>
       </c>
       <c r="B370" s="4" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C370" s="4" t="s">
         <v>1165</v>
-      </c>
-      <c r="C370" s="4" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.2">
@@ -13190,10 +13190,10 @@
         <v>370</v>
       </c>
       <c r="B371" s="4" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C371" s="4" t="s">
         <v>1167</v>
-      </c>
-      <c r="C371" s="4" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.2">
@@ -13201,10 +13201,10 @@
         <v>371</v>
       </c>
       <c r="B372" s="4" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C372" s="4" t="s">
         <v>1169</v>
-      </c>
-      <c r="C372" s="4" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
@@ -13212,10 +13212,10 @@
         <v>372</v>
       </c>
       <c r="B373" s="4" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C373" s="4" t="s">
         <v>1171</v>
-      </c>
-      <c r="C373" s="4" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
@@ -13223,10 +13223,10 @@
         <v>373</v>
       </c>
       <c r="B374" s="4" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C374" s="4" t="s">
         <v>1173</v>
-      </c>
-      <c r="C374" s="4" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.2">
@@ -13234,10 +13234,10 @@
         <v>374</v>
       </c>
       <c r="B375" s="4" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C375" s="4" t="s">
         <v>1175</v>
-      </c>
-      <c r="C375" s="4" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
@@ -13245,10 +13245,10 @@
         <v>375</v>
       </c>
       <c r="B376" s="4" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C376" s="4" t="s">
         <v>1177</v>
-      </c>
-      <c r="C376" s="4" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.2">
@@ -13256,10 +13256,10 @@
         <v>376</v>
       </c>
       <c r="B377" s="4" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C377" s="4" t="s">
         <v>1179</v>
-      </c>
-      <c r="C377" s="4" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.2">
@@ -13267,10 +13267,10 @@
         <v>377</v>
       </c>
       <c r="B378" s="4" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C378" s="4" t="s">
         <v>1181</v>
-      </c>
-      <c r="C378" s="4" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.2">
@@ -13278,10 +13278,10 @@
         <v>378</v>
       </c>
       <c r="B379" s="4" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C379" s="4" t="s">
         <v>1183</v>
-      </c>
-      <c r="C379" s="4" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.2">
@@ -13289,10 +13289,10 @@
         <v>379</v>
       </c>
       <c r="B380" s="4" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C380" s="4" t="s">
         <v>1185</v>
-      </c>
-      <c r="C380" s="4" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.2">
@@ -13300,10 +13300,10 @@
         <v>380</v>
       </c>
       <c r="B381" s="4" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C381" s="4" t="s">
         <v>1187</v>
-      </c>
-      <c r="C381" s="4" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.2">
@@ -13311,10 +13311,10 @@
         <v>381</v>
       </c>
       <c r="B382" s="4" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C382" s="4" t="s">
         <v>1189</v>
-      </c>
-      <c r="C382" s="4" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.2">
@@ -13322,10 +13322,10 @@
         <v>382</v>
       </c>
       <c r="B383" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C383" s="4" t="s">
         <v>1191</v>
-      </c>
-      <c r="C383" s="4" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
@@ -13333,10 +13333,10 @@
         <v>383</v>
       </c>
       <c r="B384" s="4" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C384" s="4" t="s">
         <v>1193</v>
-      </c>
-      <c r="C384" s="4" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
@@ -13344,10 +13344,10 @@
         <v>384</v>
       </c>
       <c r="B385" s="4" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C385" s="4" t="s">
         <v>1195</v>
-      </c>
-      <c r="C385" s="4" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.2">
@@ -13355,10 +13355,10 @@
         <v>385</v>
       </c>
       <c r="B386" s="4" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C386" s="4" t="s">
         <v>1197</v>
-      </c>
-      <c r="C386" s="4" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
@@ -13366,10 +13366,10 @@
         <v>386</v>
       </c>
       <c r="B387" s="4" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C387" s="4" t="s">
         <v>1199</v>
-      </c>
-      <c r="C387" s="4" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.2">
@@ -13377,10 +13377,10 @@
         <v>387</v>
       </c>
       <c r="B388" s="4" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C388" s="4" t="s">
         <v>1201</v>
-      </c>
-      <c r="C388" s="4" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.2">
@@ -13388,10 +13388,10 @@
         <v>388</v>
       </c>
       <c r="B389" s="4" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C389" s="4" t="s">
         <v>1203</v>
-      </c>
-      <c r="C389" s="4" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.2">
@@ -13399,10 +13399,10 @@
         <v>389</v>
       </c>
       <c r="B390" s="4" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C390" s="4" t="s">
         <v>1205</v>
-      </c>
-      <c r="C390" s="4" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.2">
@@ -13410,10 +13410,10 @@
         <v>390</v>
       </c>
       <c r="B391" s="4" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C391" s="4" t="s">
         <v>1207</v>
-      </c>
-      <c r="C391" s="4" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.2">
@@ -13421,10 +13421,10 @@
         <v>391</v>
       </c>
       <c r="B392" s="4" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C392" s="4" t="s">
         <v>1209</v>
-      </c>
-      <c r="C392" s="4" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.2">
@@ -13432,10 +13432,10 @@
         <v>392</v>
       </c>
       <c r="B393" s="4" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C393" s="4" t="s">
         <v>1211</v>
-      </c>
-      <c r="C393" s="4" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.2">
@@ -13443,10 +13443,10 @@
         <v>393</v>
       </c>
       <c r="B394" s="4" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C394" s="4" t="s">
         <v>1213</v>
-      </c>
-      <c r="C394" s="4" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
@@ -13454,10 +13454,10 @@
         <v>394</v>
       </c>
       <c r="B395" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C395" s="4" t="s">
         <v>1215</v>
-      </c>
-      <c r="C395" s="4" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
@@ -13465,10 +13465,10 @@
         <v>395</v>
       </c>
       <c r="B396" s="4" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C396" s="4" t="s">
         <v>1217</v>
-      </c>
-      <c r="C396" s="4" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.2">
@@ -13476,10 +13476,10 @@
         <v>396</v>
       </c>
       <c r="B397" s="4" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C397" s="4" t="s">
         <v>1219</v>
-      </c>
-      <c r="C397" s="4" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
@@ -13487,10 +13487,10 @@
         <v>397</v>
       </c>
       <c r="B398" s="4" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C398" s="4" t="s">
         <v>1221</v>
-      </c>
-      <c r="C398" s="4" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.2">
@@ -13498,10 +13498,10 @@
         <v>398</v>
       </c>
       <c r="B399" s="4" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C399" s="4" t="s">
         <v>1223</v>
-      </c>
-      <c r="C399" s="4" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.2">
@@ -13509,10 +13509,10 @@
         <v>399</v>
       </c>
       <c r="B400" s="4" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C400" s="4" t="s">
         <v>1225</v>
-      </c>
-      <c r="C400" s="4" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.2">
@@ -13520,10 +13520,10 @@
         <v>400</v>
       </c>
       <c r="B401" s="4" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C401" s="4" t="s">
         <v>1227</v>
-      </c>
-      <c r="C401" s="4" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.2">
@@ -13531,10 +13531,10 @@
         <v>401</v>
       </c>
       <c r="B402" s="4" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C402" s="4" t="s">
         <v>1229</v>
-      </c>
-      <c r="C402" s="4" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.2">
@@ -13542,10 +13542,10 @@
         <v>402</v>
       </c>
       <c r="B403" s="4" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C403" s="4" t="s">
         <v>1231</v>
-      </c>
-      <c r="C403" s="4" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.2">
@@ -13553,10 +13553,10 @@
         <v>403</v>
       </c>
       <c r="B404" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C404" s="4" t="s">
         <v>1233</v>
-      </c>
-      <c r="C404" s="4" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.2">
@@ -13564,10 +13564,10 @@
         <v>404</v>
       </c>
       <c r="B405" s="4" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C405" s="4" t="s">
         <v>1235</v>
-      </c>
-      <c r="C405" s="4" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
@@ -13575,10 +13575,10 @@
         <v>405</v>
       </c>
       <c r="B406" s="4" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C406" s="4" t="s">
         <v>1237</v>
-      </c>
-      <c r="C406" s="4" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
@@ -13586,10 +13586,10 @@
         <v>406</v>
       </c>
       <c r="B407" s="4" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C407" s="4" t="s">
         <v>1239</v>
-      </c>
-      <c r="C407" s="4" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.2">
@@ -13597,10 +13597,10 @@
         <v>407</v>
       </c>
       <c r="B408" s="4" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C408" s="4" t="s">
         <v>1241</v>
-      </c>
-      <c r="C408" s="4" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
@@ -13608,10 +13608,10 @@
         <v>408</v>
       </c>
       <c r="B409" s="4" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C409" s="4" t="s">
         <v>1243</v>
-      </c>
-      <c r="C409" s="4" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.2">
@@ -13619,10 +13619,10 @@
         <v>409</v>
       </c>
       <c r="B410" s="4" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C410" s="4" t="s">
         <v>1245</v>
-      </c>
-      <c r="C410" s="4" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.2">
@@ -13630,10 +13630,10 @@
         <v>410</v>
       </c>
       <c r="B411" s="4" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C411" s="4" t="s">
         <v>1247</v>
-      </c>
-      <c r="C411" s="4" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.2">
@@ -13641,10 +13641,10 @@
         <v>411</v>
       </c>
       <c r="B412" s="4" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C412" s="4" t="s">
         <v>1249</v>
-      </c>
-      <c r="C412" s="4" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.2">
@@ -13652,10 +13652,10 @@
         <v>412</v>
       </c>
       <c r="B413" s="4" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C413" s="4" t="s">
         <v>1251</v>
-      </c>
-      <c r="C413" s="4" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.2">
@@ -13663,10 +13663,10 @@
         <v>413</v>
       </c>
       <c r="B414" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C414" s="4" t="s">
         <v>1253</v>
-      </c>
-      <c r="C414" s="4" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.2">
@@ -13674,10 +13674,10 @@
         <v>414</v>
       </c>
       <c r="B415" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C415" s="4" t="s">
         <v>1255</v>
-      </c>
-      <c r="C415" s="4" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.2">
@@ -13685,10 +13685,10 @@
         <v>415</v>
       </c>
       <c r="B416" s="4" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C416" s="4" t="s">
         <v>1257</v>
-      </c>
-      <c r="C416" s="4" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.2">
@@ -13696,10 +13696,10 @@
         <v>416</v>
       </c>
       <c r="B417" s="4" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C417" s="4" t="s">
         <v>1259</v>
-      </c>
-      <c r="C417" s="4" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.2">
@@ -13707,10 +13707,10 @@
         <v>417</v>
       </c>
       <c r="B418" s="4" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C418" s="4" t="s">
         <v>1261</v>
-      </c>
-      <c r="C418" s="4" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.2">
@@ -13718,10 +13718,10 @@
         <v>418</v>
       </c>
       <c r="B419" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C419" s="4" t="s">
         <v>1263</v>
-      </c>
-      <c r="C419" s="4" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
@@ -13729,10 +13729,10 @@
         <v>419</v>
       </c>
       <c r="B420" s="4" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C420" s="4" t="s">
         <v>1265</v>
-      </c>
-      <c r="C420" s="4" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.2">
@@ -13740,10 +13740,10 @@
         <v>420</v>
       </c>
       <c r="B421" s="4" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C421" s="4" t="s">
         <v>1267</v>
-      </c>
-      <c r="C421" s="4" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.2">
@@ -13751,10 +13751,10 @@
         <v>421</v>
       </c>
       <c r="B422" s="4" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C422" s="4" t="s">
         <v>1269</v>
-      </c>
-      <c r="C422" s="4" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.2">
@@ -13762,10 +13762,10 @@
         <v>422</v>
       </c>
       <c r="B423" s="4" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C423" s="4" t="s">
         <v>1271</v>
-      </c>
-      <c r="C423" s="4" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.2">
@@ -13773,10 +13773,10 @@
         <v>423</v>
       </c>
       <c r="B424" s="4" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C424" s="4" t="s">
         <v>1273</v>
-      </c>
-      <c r="C424" s="4" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.2">
@@ -13784,10 +13784,10 @@
         <v>424</v>
       </c>
       <c r="B425" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C425" s="4" t="s">
         <v>1275</v>
-      </c>
-      <c r="C425" s="4" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.2">
@@ -13795,10 +13795,10 @@
         <v>425</v>
       </c>
       <c r="B426" s="4" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C426" s="4" t="s">
         <v>1277</v>
-      </c>
-      <c r="C426" s="4" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.2">
@@ -13806,10 +13806,10 @@
         <v>426</v>
       </c>
       <c r="B427" s="4" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C427" s="4" t="s">
         <v>1279</v>
-      </c>
-      <c r="C427" s="4" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.2">
@@ -13817,10 +13817,10 @@
         <v>427</v>
       </c>
       <c r="B428" s="4" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C428" s="4" t="s">
         <v>1281</v>
-      </c>
-      <c r="C428" s="4" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.2">
@@ -13828,10 +13828,10 @@
         <v>428</v>
       </c>
       <c r="B429" s="4" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C429" s="4" t="s">
         <v>1283</v>
-      </c>
-      <c r="C429" s="4" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.2">
@@ -13839,10 +13839,10 @@
         <v>429</v>
       </c>
       <c r="B430" s="4" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C430" s="4" t="s">
         <v>1285</v>
-      </c>
-      <c r="C430" s="4" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
@@ -13850,10 +13850,10 @@
         <v>430</v>
       </c>
       <c r="B431" s="4" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C431" s="4" t="s">
         <v>1287</v>
-      </c>
-      <c r="C431" s="4" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.2">
@@ -13861,10 +13861,10 @@
         <v>431</v>
       </c>
       <c r="B432" s="4" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C432" s="4" t="s">
         <v>1289</v>
-      </c>
-      <c r="C432" s="4" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.2">
@@ -13872,10 +13872,10 @@
         <v>432</v>
       </c>
       <c r="B433" s="4" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C433" s="4" t="s">
         <v>1291</v>
-      </c>
-      <c r="C433" s="4" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.2">
@@ -13883,10 +13883,10 @@
         <v>433</v>
       </c>
       <c r="B434" s="4" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C434" s="4" t="s">
         <v>1293</v>
-      </c>
-      <c r="C434" s="4" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.2">
@@ -13894,10 +13894,10 @@
         <v>434</v>
       </c>
       <c r="B435" s="4" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C435" s="4" t="s">
         <v>1295</v>
-      </c>
-      <c r="C435" s="4" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.2">
@@ -13905,10 +13905,10 @@
         <v>435</v>
       </c>
       <c r="B436" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C436" s="4" t="s">
         <v>1297</v>
-      </c>
-      <c r="C436" s="4" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.2">
@@ -13916,10 +13916,10 @@
         <v>436</v>
       </c>
       <c r="B437" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C437" s="4" t="s">
         <v>1299</v>
-      </c>
-      <c r="C437" s="4" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.2">
@@ -13927,10 +13927,10 @@
         <v>437</v>
       </c>
       <c r="B438" s="4" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C438" s="4" t="s">
         <v>1301</v>
-      </c>
-      <c r="C438" s="4" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.2">
@@ -13938,10 +13938,10 @@
         <v>438</v>
       </c>
       <c r="B439" s="4" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C439" s="4" t="s">
         <v>1303</v>
-      </c>
-      <c r="C439" s="4" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.2">
@@ -13949,10 +13949,10 @@
         <v>439</v>
       </c>
       <c r="B440" s="4" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C440" s="4" t="s">
         <v>1305</v>
-      </c>
-      <c r="C440" s="4" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.2">
@@ -13960,10 +13960,10 @@
         <v>440</v>
       </c>
       <c r="B441" s="4" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C441" s="4" t="s">
         <v>1307</v>
-      </c>
-      <c r="C441" s="4" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
@@ -13971,10 +13971,10 @@
         <v>441</v>
       </c>
       <c r="B442" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C442" s="4" t="s">
         <v>1309</v>
-      </c>
-      <c r="C442" s="4" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.2">
@@ -13982,10 +13982,10 @@
         <v>442</v>
       </c>
       <c r="B443" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C443" s="4" t="s">
         <v>1311</v>
-      </c>
-      <c r="C443" s="4" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.2">
@@ -13993,10 +13993,10 @@
         <v>443</v>
       </c>
       <c r="B444" s="4" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C444" s="4" t="s">
         <v>1313</v>
-      </c>
-      <c r="C444" s="4" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.2">
@@ -14004,10 +14004,10 @@
         <v>444</v>
       </c>
       <c r="B445" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C445" s="4" t="s">
         <v>1315</v>
-      </c>
-      <c r="C445" s="4" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.2">
@@ -14015,10 +14015,10 @@
         <v>445</v>
       </c>
       <c r="B446" s="4" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C446" s="4" t="s">
         <v>1317</v>
-      </c>
-      <c r="C446" s="4" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.2">
@@ -14026,10 +14026,10 @@
         <v>446</v>
       </c>
       <c r="B447" s="4" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C447" s="4" t="s">
         <v>1319</v>
-      </c>
-      <c r="C447" s="4" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.2">
@@ -14037,10 +14037,10 @@
         <v>447</v>
       </c>
       <c r="B448" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C448" s="4" t="s">
         <v>1321</v>
-      </c>
-      <c r="C448" s="4" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.2">
@@ -14048,10 +14048,10 @@
         <v>448</v>
       </c>
       <c r="B449" s="4" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C449" s="4" t="s">
         <v>1323</v>
-      </c>
-      <c r="C449" s="4" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.2">
@@ -14059,10 +14059,10 @@
         <v>449</v>
       </c>
       <c r="B450" s="4" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C450" s="4" t="s">
         <v>1325</v>
-      </c>
-      <c r="C450" s="4" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.2">
@@ -14070,10 +14070,10 @@
         <v>450</v>
       </c>
       <c r="B451" s="4" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C451" s="4" t="s">
         <v>1327</v>
-      </c>
-      <c r="C451" s="4" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.2">
@@ -14081,10 +14081,10 @@
         <v>451</v>
       </c>
       <c r="B452" s="4" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C452" s="4" t="s">
         <v>1329</v>
-      </c>
-      <c r="C452" s="4" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
@@ -14092,10 +14092,10 @@
         <v>452</v>
       </c>
       <c r="B453" s="4" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C453" s="4" t="s">
         <v>1331</v>
-      </c>
-      <c r="C453" s="4" t="s">
-        <v>1332</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.2">
@@ -14103,10 +14103,10 @@
         <v>453</v>
       </c>
       <c r="B454" s="4" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C454" s="4" t="s">
         <v>1333</v>
-      </c>
-      <c r="C454" s="4" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.2">
@@ -14114,10 +14114,10 @@
         <v>454</v>
       </c>
       <c r="B455" s="4" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C455" s="4" t="s">
         <v>1335</v>
-      </c>
-      <c r="C455" s="4" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.2">
@@ -14125,10 +14125,10 @@
         <v>455</v>
       </c>
       <c r="B456" s="4" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C456" s="4" t="s">
         <v>1337</v>
-      </c>
-      <c r="C456" s="4" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.2">
@@ -14136,10 +14136,10 @@
         <v>456</v>
       </c>
       <c r="B457" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C457" s="4" t="s">
         <v>1339</v>
-      </c>
-      <c r="C457" s="4" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.2">
@@ -14147,10 +14147,10 @@
         <v>457</v>
       </c>
       <c r="B458" s="4" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C458" s="4" t="s">
         <v>1341</v>
-      </c>
-      <c r="C458" s="4" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.2">
@@ -14158,10 +14158,10 @@
         <v>458</v>
       </c>
       <c r="B459" s="4" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C459" s="4" t="s">
         <v>1343</v>
-      </c>
-      <c r="C459" s="4" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.2">
@@ -14169,10 +14169,10 @@
         <v>459</v>
       </c>
       <c r="B460" s="4" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C460" s="4" t="s">
         <v>1345</v>
-      </c>
-      <c r="C460" s="4" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.2">
@@ -14180,10 +14180,10 @@
         <v>460</v>
       </c>
       <c r="B461" s="4" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C461" s="4" t="s">
         <v>1347</v>
-      </c>
-      <c r="C461" s="4" t="s">
-        <v>1348</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.2">
@@ -14191,10 +14191,10 @@
         <v>461</v>
       </c>
       <c r="B462" s="4" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C462" s="4" t="s">
         <v>1349</v>
-      </c>
-      <c r="C462" s="4" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.2">
@@ -14202,10 +14202,10 @@
         <v>462</v>
       </c>
       <c r="B463" s="4" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C463" s="4" t="s">
         <v>1351</v>
-      </c>
-      <c r="C463" s="4" t="s">
-        <v>1352</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
@@ -14213,10 +14213,10 @@
         <v>463</v>
       </c>
       <c r="B464" s="4" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C464" s="4" t="s">
         <v>1353</v>
-      </c>
-      <c r="C464" s="4" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.2">
@@ -14224,10 +14224,10 @@
         <v>464</v>
       </c>
       <c r="B465" s="4" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C465" s="4" t="s">
         <v>1355</v>
-      </c>
-      <c r="C465" s="4" t="s">
-        <v>1356</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.2">
@@ -14235,10 +14235,10 @@
         <v>465</v>
       </c>
       <c r="B466" s="4" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C466" s="4" t="s">
         <v>1357</v>
-      </c>
-      <c r="C466" s="4" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.2">
@@ -14246,10 +14246,10 @@
         <v>466</v>
       </c>
       <c r="B467" s="4" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C467" s="4" t="s">
         <v>1359</v>
-      </c>
-      <c r="C467" s="4" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.2">
@@ -14257,10 +14257,10 @@
         <v>467</v>
       </c>
       <c r="B468" s="4" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C468" s="4" t="s">
         <v>1361</v>
-      </c>
-      <c r="C468" s="4" t="s">
-        <v>1362</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.2">
@@ -14268,10 +14268,10 @@
         <v>468</v>
       </c>
       <c r="B469" s="4" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C469" s="4" t="s">
         <v>1363</v>
-      </c>
-      <c r="C469" s="4" t="s">
-        <v>1364</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.2">
@@ -14279,10 +14279,10 @@
         <v>469</v>
       </c>
       <c r="B470" s="4" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C470" s="4" t="s">
         <v>1365</v>
-      </c>
-      <c r="C470" s="4" t="s">
-        <v>1366</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.2">
@@ -14290,10 +14290,10 @@
         <v>470</v>
       </c>
       <c r="B471" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C471" s="4" t="s">
         <v>1367</v>
-      </c>
-      <c r="C471" s="4" t="s">
-        <v>1368</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.2">
@@ -14301,10 +14301,10 @@
         <v>471</v>
       </c>
       <c r="B472" s="4" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C472" s="4" t="s">
         <v>1369</v>
-      </c>
-      <c r="C472" s="4" t="s">
-        <v>1370</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.2">
@@ -14312,10 +14312,10 @@
         <v>472</v>
       </c>
       <c r="B473" s="4" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C473" s="4" t="s">
         <v>1371</v>
-      </c>
-      <c r="C473" s="4" t="s">
-        <v>1372</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.2">
@@ -14323,10 +14323,10 @@
         <v>473</v>
       </c>
       <c r="B474" s="4" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C474" s="4" t="s">
         <v>1373</v>
-      </c>
-      <c r="C474" s="4" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
@@ -14334,10 +14334,10 @@
         <v>474</v>
       </c>
       <c r="B475" s="4" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C475" s="4" t="s">
         <v>1375</v>
-      </c>
-      <c r="C475" s="4" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.2">
@@ -14345,10 +14345,10 @@
         <v>475</v>
       </c>
       <c r="B476" s="4" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C476" s="4" t="s">
         <v>1377</v>
-      </c>
-      <c r="C476" s="4" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.2">
@@ -14356,10 +14356,10 @@
         <v>476</v>
       </c>
       <c r="B477" s="4" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C477" s="4" t="s">
         <v>1379</v>
-      </c>
-      <c r="C477" s="4" t="s">
-        <v>1380</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.2">
@@ -14367,10 +14367,10 @@
         <v>477</v>
       </c>
       <c r="B478" s="4" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C478" s="4" t="s">
         <v>1381</v>
-      </c>
-      <c r="C478" s="4" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.2">
@@ -14378,10 +14378,10 @@
         <v>478</v>
       </c>
       <c r="B479" s="4" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C479" s="4" t="s">
         <v>1383</v>
-      </c>
-      <c r="C479" s="4" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.2">
@@ -14389,10 +14389,10 @@
         <v>479</v>
       </c>
       <c r="B480" s="4" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C480" s="4" t="s">
         <v>1385</v>
-      </c>
-      <c r="C480" s="4" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.2">
@@ -14400,10 +14400,10 @@
         <v>480</v>
       </c>
       <c r="B481" s="4" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C481" s="4" t="s">
         <v>1387</v>
-      </c>
-      <c r="C481" s="4" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.2">
@@ -14411,10 +14411,10 @@
         <v>481</v>
       </c>
       <c r="B482" s="4" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C482" s="4" t="s">
         <v>1389</v>
-      </c>
-      <c r="C482" s="4" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.2">
@@ -14422,10 +14422,10 @@
         <v>482</v>
       </c>
       <c r="B483" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C483" s="4" t="s">
         <v>1391</v>
-      </c>
-      <c r="C483" s="4" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
@@ -14433,10 +14433,10 @@
         <v>483</v>
       </c>
       <c r="B484" s="4" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C484" s="4" t="s">
         <v>1393</v>
-      </c>
-      <c r="C484" s="4" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.2">
@@ -14444,10 +14444,10 @@
         <v>484</v>
       </c>
       <c r="B485" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C485" s="4" t="s">
         <v>1395</v>
-      </c>
-      <c r="C485" s="4" t="s">
-        <v>1396</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
@@ -14455,10 +14455,10 @@
         <v>485</v>
       </c>
       <c r="B486" s="4" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C486" s="4" t="s">
         <v>1397</v>
-      </c>
-      <c r="C486" s="4" t="s">
-        <v>1398</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.2">
@@ -14466,10 +14466,10 @@
         <v>486</v>
       </c>
       <c r="B487" s="4" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C487" s="4" t="s">
         <v>1399</v>
-      </c>
-      <c r="C487" s="4" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.2">
@@ -14477,10 +14477,10 @@
         <v>487</v>
       </c>
       <c r="B488" s="4" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C488" s="4" t="s">
         <v>1401</v>
-      </c>
-      <c r="C488" s="4" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.2">
@@ -14488,10 +14488,10 @@
         <v>488</v>
       </c>
       <c r="B489" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C489" s="4" t="s">
         <v>1403</v>
-      </c>
-      <c r="C489" s="4" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.2">
@@ -14499,10 +14499,10 @@
         <v>489</v>
       </c>
       <c r="B490" s="4" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C490" s="4" t="s">
         <v>1405</v>
-      </c>
-      <c r="C490" s="4" t="s">
-        <v>1406</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.2">
@@ -14510,10 +14510,10 @@
         <v>490</v>
       </c>
       <c r="B491" s="4" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C491" s="4" t="s">
         <v>1407</v>
-      </c>
-      <c r="C491" s="4" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.2">
@@ -14521,10 +14521,10 @@
         <v>491</v>
       </c>
       <c r="B492" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C492" s="4" t="s">
         <v>1409</v>
-      </c>
-      <c r="C492" s="4" t="s">
-        <v>1410</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.2">
@@ -14532,10 +14532,10 @@
         <v>492</v>
       </c>
       <c r="B493" s="4" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C493" s="4" t="s">
         <v>1411</v>
-      </c>
-      <c r="C493" s="4" t="s">
-        <v>1412</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.2">
@@ -14543,10 +14543,10 @@
         <v>493</v>
       </c>
       <c r="B494" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C494" s="4" t="s">
         <v>1413</v>
-      </c>
-      <c r="C494" s="4" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
@@ -14554,10 +14554,10 @@
         <v>494</v>
       </c>
       <c r="B495" s="4" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C495" s="4" t="s">
         <v>1415</v>
-      </c>
-      <c r="C495" s="4" t="s">
-        <v>1416</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.2">
@@ -14565,10 +14565,10 @@
         <v>495</v>
       </c>
       <c r="B496" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C496" s="4" t="s">
         <v>1417</v>
-      </c>
-      <c r="C496" s="4" t="s">
-        <v>1418</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
@@ -14576,10 +14576,10 @@
         <v>496</v>
       </c>
       <c r="B497" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C497" s="4" t="s">
         <v>1419</v>
-      </c>
-      <c r="C497" s="4" t="s">
-        <v>1420</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.2">
@@ -14587,10 +14587,10 @@
         <v>497</v>
       </c>
       <c r="B498" s="4" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C498" s="4" t="s">
         <v>1421</v>
-      </c>
-      <c r="C498" s="4" t="s">
-        <v>1422</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.2">
@@ -14598,10 +14598,10 @@
         <v>498</v>
       </c>
       <c r="B499" s="4" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C499" s="4" t="s">
         <v>1423</v>
-      </c>
-      <c r="C499" s="4" t="s">
-        <v>1424</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.2">
@@ -14609,10 +14609,10 @@
         <v>499</v>
       </c>
       <c r="B500" s="4" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C500" s="4" t="s">
         <v>1425</v>
-      </c>
-      <c r="C500" s="4" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.2">
@@ -14620,10 +14620,10 @@
         <v>500</v>
       </c>
       <c r="B501" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C501" s="4" t="s">
         <v>1427</v>
-      </c>
-      <c r="C501" s="4" t="s">
-        <v>1428</v>
       </c>
     </row>
   </sheetData>
@@ -14646,19 +14646,19 @@
         <v>43</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -14666,10 +14666,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>399</v>
       </c>
       <c r="D2" s="4">
         <v>5.72</v>
@@ -14678,7 +14678,7 @@
         <v>6.98</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -14686,10 +14686,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>402</v>
       </c>
       <c r="D3" s="4">
         <v>2.76</v>
@@ -14698,7 +14698,7 @@
         <v>3.86</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -14706,10 +14706,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>404</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>405</v>
       </c>
       <c r="D4" s="4">
         <v>17.420000000000002</v>
@@ -14718,7 +14718,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -14726,10 +14726,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>407</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>408</v>
       </c>
       <c r="D5" s="4">
         <v>2.74</v>
@@ -14738,7 +14738,7 @@
         <v>3.44</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -14746,10 +14746,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>411</v>
       </c>
       <c r="D6" s="4">
         <v>1.68</v>
@@ -14758,7 +14758,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -14766,10 +14766,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>414</v>
       </c>
       <c r="D7" s="4">
         <v>2.08</v>
@@ -14778,7 +14778,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -14786,10 +14786,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>417</v>
       </c>
       <c r="D8" s="4">
         <v>2.98</v>
@@ -14798,7 +14798,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -14806,10 +14806,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>419</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>420</v>
       </c>
       <c r="D9" s="4">
         <v>2.98</v>
@@ -14818,7 +14818,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -14826,10 +14826,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>423</v>
       </c>
       <c r="D10" s="4">
         <v>248</v>
@@ -14838,7 +14838,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -14846,10 +14846,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>426</v>
       </c>
       <c r="D11" s="4">
         <v>17.98</v>
@@ -14858,7 +14858,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -14896,19 +14896,19 @@
         <v>43</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>1429</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>1430</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>1431</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>1432</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>1433</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -14922,7 +14922,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="E2" s="7">
         <v>45072.29583333333</v>
@@ -14942,7 +14942,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E3" s="7">
         <v>45072.29583333333</v>
@@ -14962,7 +14962,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E4" s="7">
         <v>45072.29583333333</v>
@@ -14982,7 +14982,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="E5" s="7">
         <v>45072.29583333333</v>
@@ -15002,7 +15002,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="E6" s="7">
         <v>45072.29583333333</v>
@@ -15022,7 +15022,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="E7" s="7">
         <v>45072.29583333333</v>
@@ -15042,7 +15042,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="E8" s="7">
         <v>45072.29583333333</v>
@@ -15062,7 +15062,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="E9" s="7">
         <v>45072.29583333333</v>
@@ -15082,7 +15082,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="E10" s="7">
         <v>45072.29583333333</v>
@@ -15102,7 +15102,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="E11" s="7">
         <v>45072.29583333333</v>
@@ -15122,7 +15122,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="E12" s="7">
         <v>45072.29583333333</v>
@@ -15142,7 +15142,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E13" s="7">
         <v>45072.29583333333</v>
@@ -15162,7 +15162,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E14" s="7">
         <v>45072.29583333333</v>
@@ -15182,7 +15182,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="E15" s="7">
         <v>45072.29583333333</v>
@@ -15202,7 +15202,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="E16" s="7">
         <v>45072.29583333333</v>
@@ -15222,7 +15222,7 @@
         <v>6</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="E17" s="7">
         <v>45072.29583333333</v>
@@ -15242,7 +15242,7 @@
         <v>7</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="E18" s="7">
         <v>45072.29583333333</v>
@@ -15262,7 +15262,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="E19" s="7">
         <v>45072.29583333333</v>
@@ -15282,7 +15282,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="E20" s="7">
         <v>45072.29583333333</v>
@@ -15302,7 +15302,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="E21" s="7">
         <v>45072.29583333333</v>
@@ -15322,7 +15322,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="E22" s="7">
         <v>45072.29583333333</v>
@@ -15342,7 +15342,7 @@
         <v>2</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E23" s="7">
         <v>45072.29583333333</v>
@@ -15362,7 +15362,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E24" s="7">
         <v>45072.29583333333</v>
@@ -15382,7 +15382,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="E25" s="7">
         <v>45072.29583333333</v>
@@ -15402,7 +15402,7 @@
         <v>5</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="E26" s="7">
         <v>45072.29583333333</v>
@@ -15422,7 +15422,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="E27" s="7">
         <v>45072.29583333333</v>
@@ -15442,7 +15442,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="E28" s="7">
         <v>45072.29583333333</v>
@@ -15462,7 +15462,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="E29" s="7">
         <v>45072.29583333333</v>
@@ -15482,7 +15482,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="E30" s="7">
         <v>45072.29583333333</v>
@@ -15502,7 +15502,7 @@
         <v>10</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="E31" s="7">
         <v>45072.29583333333</v>
@@ -15522,7 +15522,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="E32" s="7">
         <v>45072.29583333333</v>
@@ -15542,7 +15542,7 @@
         <v>2</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E33" s="7">
         <v>45072.29583333333</v>
@@ -15562,7 +15562,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E34" s="7">
         <v>45072.29583333333</v>
@@ -15582,7 +15582,7 @@
         <v>4</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="E35" s="7">
         <v>45072.29583333333</v>
@@ -15602,7 +15602,7 @@
         <v>5</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="E36" s="7">
         <v>45072.29583333333</v>
@@ -15622,7 +15622,7 @@
         <v>6</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="E37" s="7">
         <v>45072.29583333333</v>
@@ -15642,7 +15642,7 @@
         <v>7</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="E38" s="7">
         <v>45072.29583333333</v>
@@ -15662,7 +15662,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="E39" s="7">
         <v>45072.29583333333</v>
@@ -15682,7 +15682,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="E40" s="7">
         <v>45072.29583333333</v>
@@ -15702,7 +15702,7 @@
         <v>10</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="E41" s="7">
         <v>45072.29583333333</v>
@@ -15742,10 +15742,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="C2" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -15753,10 +15753,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="C3" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -15764,10 +15764,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="C4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -15775,10 +15775,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="C5" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -15786,10 +15786,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="C6" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
   </sheetData>
@@ -15842,7 +15842,7 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -15887,7 +15887,7 @@
         <v>13</v>
       </c>
       <c r="F1" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G1" t="s">
         <v>8</v>
@@ -15916,7 +15916,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -15942,7 +15942,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -15968,7 +15968,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -15994,7 +15994,7 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -16058,7 +16058,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -16081,7 +16081,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="G3">
         <v>1</v>

--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\jdbc\finance\acct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BE7CCB-8DA9-4C39-B6C7-0CDC63C2030A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458A61BD-1FDB-4AA1-AFCC-E99B9E154C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="6" activeTab="10" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="t_product" sheetId="4" r:id="rId4"/>
     <sheet name="t_company_product" sheetId="13" r:id="rId5"/>
     <sheet name="t_warehouse" sheetId="6" r:id="rId6"/>
-    <sheet name="t_sales_order" sheetId="5" r:id="rId7"/>
+    <sheet name="t_order" sheetId="5" r:id="rId7"/>
     <sheet name="t_billof_product" sheetId="7" r:id="rId8"/>
     <sheet name="t_freight_order" sheetId="8" r:id="rId9"/>
     <sheet name="t_payment" sheetId="9" r:id="rId10"/>

--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\jdbc\finance\acct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458A61BD-1FDB-4AA1-AFCC-E99B9E154C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E290B696-A890-452F-A27D-8B17F31B53E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="6" activeTab="10" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="3" activeTab="4" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
   </bookViews>
   <sheets>
     <sheet name="t_user" sheetId="1" r:id="rId1"/>
@@ -4850,18 +4850,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"items":[{"id":1,"price":1,"quantity":1},{"id":2,"price":1.5,"quantity":2}]}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"items":[{"id":1,"price":1,"quantity":1},{"id":2,"price":1.5,"quantity":2},{"id":3,"price":3,"quantity":3.5}]}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"items":[{"id":3,"price":3,"quantity":3.5}]}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>freight_order_id</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4871,6 +4859,18 @@
   </si>
   <si>
     <t>t_order</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"items":[{"id":11,"price":1,"quantity":1},{"id":12,"price":1.5,"quantity":2},{"id":13,"price":3,"quantity":3.5}]}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"items":[{"id":11,"price":1,"quantity":1},{"id":12,"price":1.5,"quantity":2}]}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"items":[{"id":13,"price":3,"quantity":3.5}]}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5358,7 +5358,7 @@
         <v>33</v>
       </c>
       <c r="F1" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="G1" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -5413,7 +5413,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -5466,7 +5466,7 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="D2" t="s">
         <v>21</v>
@@ -5486,7 +5486,7 @@
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
@@ -5506,7 +5506,7 @@
         <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
@@ -5526,7 +5526,7 @@
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
@@ -15842,7 +15842,7 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -15887,7 +15887,7 @@
         <v>13</v>
       </c>
       <c r="F1" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="G1" t="s">
         <v>8</v>
@@ -15916,7 +15916,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -15942,7 +15942,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -15968,7 +15968,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -15994,7 +15994,7 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -16058,7 +16058,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -16081,7 +16081,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="G3">
         <v>1</v>

--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\mymall\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887C852C-E5DD-4039-B1F2-1FCF977006EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3367B98-B172-4156-868C-24E52572C2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="10" activeTab="15" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="10" activeTab="13" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
   </bookViews>
   <sheets>
     <sheet name="t_user" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2307" uniqueCount="1625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2327" uniqueCount="1633">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5445,6 +5445,38 @@
   </si>
   <si>
     <t>issuer_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发票签发人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发票接收人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>收据签发人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>收据接收人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>付款人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>收款人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>订单乙方/卖方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>订单甲方/买方</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5573,6 +5605,2020 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>28574</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="文本框 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86714732-1425-E54E-984F-F1CB8F43FA72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5276850" y="28574"/>
+          <a:ext cx="8286750" cy="1247775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>policy0001</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>的经济交易处理流程（物流与财流）：</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>1)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            <a:t>甲方</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>parta</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>与 乙方</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0"/>
+            <a:t>partb </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>签订订单</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0"/>
+            <a:t>:t_order, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>parta</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>准备收货</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,parb</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>准备发货，从此交易开始。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>乙方</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>partb </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>发货</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>签出货物发票</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:t_billof_product/invoice,  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>甲方据发票登记材料采购。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>乙方</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>partb </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>物流运输</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>签出货运单</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:t_freight_order,  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>甲方</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>据运单</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>登记</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>在途物资。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>甲方签出货物收据</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:t_billof_product/receipt,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>乙</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>方将</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>收据</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>登记为</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>业务成本。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>5) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>甲方</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>签发付款单</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:t_payment,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>甲方支付货款</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>乙方</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>据付款单应收转实收</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>至此交易结束。</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="文本框 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{671A9820-DD1E-D21F-FD3E-08978599F26A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5276850" y="1323974"/>
+          <a:ext cx="8286750" cy="2314575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>公司日常经济活动的各种记账凭证：是会计记账的基础与依据</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>--</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>核算原理</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>根据指定的</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>company_id</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>即当前的核算主体</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>id</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>亦即会计凭证的持有主体，通过其在经济业务中与订单</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>收发单</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>付款单之间</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>的相互关系来确定会计科目的持有头寸。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>会计策略是一个由</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>'</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>策略名</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>/</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>科目持有头寸</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>'</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>的名称路径，可通过编制</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>select</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>语句的</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>position</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>字段来实现会计策略与记账凭证的对应</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-- position</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>即核算主体的科目持有头寸是记账逻辑的主控字段</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>基本编制原则是以实物产品立场</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>即是否获得产品的角度</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>交付空</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>持有多</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>持有产品</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>支付货币</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>为多头</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>交付产品</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>获得货币</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>为空头</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>; </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>获得货币</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>交付产品</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>为空头</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>支付货币</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>获得产品</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>为多头。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>具体而言，核算主体对待各个单据或者说记账凭证的持有科目头寸定义如下：</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>空头</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>short:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>发票的签发人</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>partb,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>收据的接收人</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>partb,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>订单卖方</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>(partb,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>订单乙方</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>), </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>付款单收款人也就是订单卖方</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>partb</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>多头</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>long:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>发票的接收人</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>parta,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>收据的签发人</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>parta,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>订单买方</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>(parta,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>订单甲方</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>), </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>付款单付款人也就是订单买方</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>parta</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>简而言之</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>就是核算主体</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>id</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>若是订单的</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>partb</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>即卖方空头持有会计科目头寸</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>若是买方</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>parta</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>则多持有会计科目头寸。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6705,7 +8751,7 @@
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="81.875" customWidth="1"/>
     <col min="5" max="5" width="9.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
@@ -6758,18 +8804,20 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A491D504-AE09-4D14-BD7B-F95BC5DE2CC2}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.75" customWidth="1"/>
+    <col min="7" max="7" width="57.375" customWidth="1"/>
     <col min="8" max="8" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6794,8 +8842,11 @@
       <c r="H1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6820,8 +8871,11 @@
       <c r="H2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6846,8 +8900,11 @@
       <c r="H3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6872,8 +8929,11 @@
       <c r="H4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6897,6 +8957,9 @@
       </c>
       <c r="H5">
         <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>45296.99722222222</v>
       </c>
     </row>
   </sheetData>
@@ -6908,7 +8971,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F73FA18-B987-444A-B339-09CE35D7E8C2}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -6916,10 +8979,11 @@
     <col min="4" max="4" width="13.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11.125" customWidth="1"/>
+    <col min="7" max="7" width="56.875" customWidth="1"/>
+    <col min="9" max="9" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6944,8 +9008,11 @@
       <c r="H1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6970,8 +9037,11 @@
       <c r="H2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6995,6 +9065,9 @@
       </c>
       <c r="H3">
         <v>1</v>
+      </c>
+      <c r="I3" s="1">
+        <v>45296.99722222222</v>
       </c>
     </row>
   </sheetData>
@@ -7005,7 +9078,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B9F82DD-9D92-4BA2-A7FE-9114B3F1FED4}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -7013,10 +9086,11 @@
     <col min="3" max="3" width="9.625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="9.625" customWidth="1"/>
     <col min="6" max="6" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="56.375" customWidth="1"/>
+    <col min="9" max="9" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7041,8 +9115,11 @@
       <c r="H1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7067,8 +9144,11 @@
       <c r="H2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7092,6 +9172,9 @@
       </c>
       <c r="H3">
         <v>1</v>
+      </c>
+      <c r="I3" s="1">
+        <v>45296.99722222222</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +9185,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D2F96A-1206-4BE2-BA64-3DDEC9C031F1}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
@@ -7111,9 +9194,10 @@
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7132,8 +9216,11 @@
       <c r="F1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" s="3" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7152,8 +9239,11 @@
       <c r="F2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7172,8 +9262,11 @@
       <c r="F3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7192,8 +9285,11 @@
       <c r="F4" t="s">
         <v>1621</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -7212,8 +9308,11 @@
       <c r="F5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G5" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -7232,8 +9331,11 @@
       <c r="F6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -7252,8 +9354,11 @@
       <c r="F7" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G7" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -7272,8 +9377,11 @@
       <c r="F8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G8" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -7292,8 +9400,11 @@
       <c r="F9" t="s">
         <v>1621</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G9" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -7310,10 +9421,13 @@
         <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1620</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -7330,10 +9444,13 @@
         <v>20</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -7350,10 +9467,13 @@
         <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>1620</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -7370,10 +9490,13 @@
         <v>20</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -7392,8 +9515,11 @@
       <c r="F14" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -7412,8 +9538,11 @@
       <c r="F15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G15" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -7432,8 +9561,11 @@
       <c r="F16" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G16" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -7451,11 +9583,16 @@
       </c>
       <c r="F17" t="s">
         <v>28</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1629</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7464,6 +9601,12 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7530,7 +9673,10 @@
   <dimension ref="A1:F164"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.375" customWidth="1"/>
+    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -11654,10 +13800,10 @@
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.375" customWidth="1"/>
+    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -11677,13 +13823,13 @@
         <v>1524</v>
       </c>
       <c r="F1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1513</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -11702,14 +13848,14 @@
       <c r="E2" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="G2" s="5">
+      <c r="H2" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -11728,14 +13874,14 @@
       <c r="E3" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="G3" s="5">
+      <c r="H3" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -11754,14 +13900,14 @@
       <c r="E4" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="s">
+        <v>1520</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
-      <c r="G4" s="5">
+      <c r="H4" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1520</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -11780,14 +13926,14 @@
       <c r="E5" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="s">
+        <v>1519</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="G5" s="5">
+      <c r="H5" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1519</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -11806,14 +13952,14 @@
       <c r="E6" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="s">
+        <v>1521</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
-      <c r="G6" s="5">
+      <c r="H6" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1521</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -11832,14 +13978,14 @@
       <c r="E7" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="s">
+        <v>1522</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="G7" s="5">
+      <c r="H7" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1522</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -11858,14 +14004,14 @@
       <c r="E8" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="s">
+        <v>1523</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="G8" s="5">
+      <c r="H8" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H8" t="s">
-        <v>1523</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -11884,14 +14030,14 @@
       <c r="E9" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="s">
+        <v>1517</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
-      <c r="G9" s="5">
+      <c r="H9" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H9" t="s">
-        <v>1517</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -11910,14 +14056,14 @@
       <c r="E10" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
-      <c r="G10" s="5">
+      <c r="H10" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H10" t="s">
-        <v>1527</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -11936,14 +14082,14 @@
       <c r="E11" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="s">
+        <v>1530</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
-      <c r="G11" s="5">
+      <c r="H11" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H11" t="s">
-        <v>1530</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -11962,14 +14108,14 @@
       <c r="E12" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G12">
         <v>1</v>
       </c>
-      <c r="G12" s="5">
+      <c r="H12" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H12" t="s">
-        <v>1535</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -11988,14 +14134,14 @@
       <c r="E13" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="s">
+        <v>1536</v>
+      </c>
+      <c r="G13">
         <v>1</v>
       </c>
-      <c r="G13" s="5">
+      <c r="H13" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H13" t="s">
-        <v>1536</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -12014,14 +14160,14 @@
       <c r="E14" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="s">
+        <v>1537</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
-      <c r="G14" s="5">
+      <c r="H14" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H14" t="s">
-        <v>1537</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -12040,14 +14186,14 @@
       <c r="E15" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="s">
+        <v>1538</v>
+      </c>
+      <c r="G15">
         <v>1</v>
       </c>
-      <c r="G15" s="5">
+      <c r="H15" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H15" t="s">
-        <v>1538</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -12066,14 +14212,14 @@
       <c r="E16" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="s">
+        <v>1533</v>
+      </c>
+      <c r="G16">
         <v>1</v>
       </c>
-      <c r="G16" s="5">
+      <c r="H16" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H16" t="s">
-        <v>1533</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -12092,14 +14238,14 @@
       <c r="E17" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="s">
+        <v>1531</v>
+      </c>
+      <c r="G17">
         <v>1</v>
       </c>
-      <c r="G17" s="5">
+      <c r="H17" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H17" t="s">
-        <v>1531</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -12118,14 +14264,14 @@
       <c r="E18" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="s">
+        <v>1539</v>
+      </c>
+      <c r="G18">
         <v>1</v>
       </c>
-      <c r="G18" s="5">
+      <c r="H18" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H18" t="s">
-        <v>1539</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -12144,14 +14290,14 @@
       <c r="E19" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="s">
+        <v>1540</v>
+      </c>
+      <c r="G19">
         <v>1</v>
       </c>
-      <c r="G19" s="5">
+      <c r="H19" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H19" t="s">
-        <v>1540</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -12170,14 +14316,14 @@
       <c r="E20" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="s">
+        <v>1541</v>
+      </c>
+      <c r="G20">
         <v>1</v>
       </c>
-      <c r="G20" s="5">
+      <c r="H20" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H20" t="s">
-        <v>1541</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -12196,14 +14342,14 @@
       <c r="E21" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="s">
+        <v>1532</v>
+      </c>
+      <c r="G21">
         <v>1</v>
       </c>
-      <c r="G21" s="5">
+      <c r="H21" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H21" t="s">
-        <v>1532</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -12222,14 +14368,14 @@
       <c r="E22" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="s">
+        <v>1528</v>
+      </c>
+      <c r="G22">
         <v>1</v>
       </c>
-      <c r="G22" s="5">
+      <c r="H22" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H22" t="s">
-        <v>1528</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -12248,14 +14394,14 @@
       <c r="E23" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="s">
+        <v>1534</v>
+      </c>
+      <c r="G23">
         <v>1</v>
       </c>
-      <c r="G23" s="5">
+      <c r="H23" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H23" t="s">
-        <v>1534</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -12274,14 +14420,14 @@
       <c r="E24" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="s">
+        <v>1543</v>
+      </c>
+      <c r="G24">
         <v>1</v>
       </c>
-      <c r="G24" s="5">
+      <c r="H24" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H24" t="s">
-        <v>1543</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -12300,14 +14446,14 @@
       <c r="E25" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="s">
+        <v>1542</v>
+      </c>
+      <c r="G25">
         <v>1</v>
       </c>
-      <c r="G25" s="5">
+      <c r="H25" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H25" t="s">
-        <v>1542</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -12326,14 +14472,14 @@
       <c r="E26" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="s">
+        <v>1529</v>
+      </c>
+      <c r="G26">
         <v>1</v>
       </c>
-      <c r="G26" s="5">
+      <c r="H26" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H26" t="s">
-        <v>1529</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -12352,14 +14498,14 @@
       <c r="E27" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G27">
         <v>1</v>
       </c>
-      <c r="G27" s="5">
+      <c r="H27" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H27" t="s">
-        <v>1544</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -12378,14 +14524,14 @@
       <c r="E28" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="s">
+        <v>1545</v>
+      </c>
+      <c r="G28">
         <v>1</v>
       </c>
-      <c r="G28" s="5">
+      <c r="H28" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H28" t="s">
-        <v>1545</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -12404,14 +14550,14 @@
       <c r="E29" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="s">
+        <v>1546</v>
+      </c>
+      <c r="G29">
         <v>1</v>
       </c>
-      <c r="G29" s="5">
+      <c r="H29" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H29" t="s">
-        <v>1546</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -12430,14 +14576,14 @@
       <c r="E30" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="s">
+        <v>1547</v>
+      </c>
+      <c r="G30">
         <v>1</v>
       </c>
-      <c r="G30" s="5">
+      <c r="H30" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H30" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -12456,14 +14602,14 @@
       <c r="E31" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="s">
+        <v>1548</v>
+      </c>
+      <c r="G31">
         <v>1</v>
       </c>
-      <c r="G31" s="5">
+      <c r="H31" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H31" t="s">
-        <v>1548</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -12482,14 +14628,14 @@
       <c r="E32" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="s">
+        <v>1549</v>
+      </c>
+      <c r="G32">
         <v>1</v>
       </c>
-      <c r="G32" s="5">
+      <c r="H32" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H32" t="s">
-        <v>1549</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -12508,14 +14654,14 @@
       <c r="E33" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G33">
         <v>1</v>
       </c>
-      <c r="G33" s="5">
+      <c r="H33" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="H33" t="s">
-        <v>1550</v>
       </c>
     </row>
   </sheetData>
@@ -12538,9 +14684,9 @@
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -12554,13 +14700,13 @@
         <v>1524</v>
       </c>
       <c r="D1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1513</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -12573,14 +14719,14 @@
       <c r="C2" t="s">
         <v>1553</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="E2" s="5">
+      <c r="F2" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1561</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -12593,14 +14739,14 @@
       <c r="C3" t="s">
         <v>1563</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="s">
+        <v>1562</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="E3" s="5">
+      <c r="F3" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1562</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -12613,14 +14759,14 @@
       <c r="C4" t="s">
         <v>1554</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="s">
+        <v>1565</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="E4" s="5">
+      <c r="F4" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1565</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -12633,14 +14779,14 @@
       <c r="C5" t="s">
         <v>1566</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="E5" s="5">
+      <c r="F5" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1564</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -12653,14 +14799,14 @@
       <c r="C6" t="s">
         <v>1568</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="E6" s="5">
+      <c r="F6" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -12673,14 +14819,14 @@
       <c r="C7" t="s">
         <v>1570</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="E7" s="5">
+      <c r="F7" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1569</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -12693,14 +14839,14 @@
       <c r="C8" t="s">
         <v>1555</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="s">
+        <v>1556</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="E8" s="5">
+      <c r="F8" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1556</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -12713,14 +14859,14 @@
       <c r="C9" t="s">
         <v>1557</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="E9" s="5">
+      <c r="F9" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1559</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -12733,14 +14879,14 @@
       <c r="C10" t="s">
         <v>1558</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E10">
         <v>1</v>
       </c>
-      <c r="E10" s="5">
+      <c r="F10" s="5">
         <v>45303.078472222223</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1560</v>
       </c>
     </row>
   </sheetData>
@@ -12753,6 +14899,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BBF8B56-2AC9-4699-A381-0BD6AF1E65F6}">
   <dimension ref="A1:C501"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
@@ -18279,6 +20430,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DF16463-48C8-4AAF-8670-417CA0ABD58B}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
@@ -19361,6 +21515,7 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.625" bestFit="1" customWidth="1"/>
   </cols>
@@ -19442,6 +21597,7 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.875" bestFit="1" customWidth="1"/>

--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\mymall\api\model\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\jdbc\finance\acct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3367B98-B172-4156-868C-24E52572C2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3003B0-B8C9-4FCF-BC6B-6B4EFB41EA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="10" activeTab="13" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="2" activeTab="5" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
   </bookViews>
   <sheets>
     <sheet name="t_user" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,19 @@
     <sheet name="t_role" sheetId="14" r:id="rId3"/>
     <sheet name="t_permission" sheetId="15" r:id="rId4"/>
     <sheet name="t_company" sheetId="3" r:id="rId5"/>
-    <sheet name="t_product" sheetId="4" r:id="rId6"/>
-    <sheet name="t_company_product" sheetId="13" r:id="rId7"/>
-    <sheet name="t_warehouse" sheetId="6" r:id="rId8"/>
-    <sheet name="t_company_warehouse" sheetId="16" r:id="rId9"/>
-    <sheet name="t_order" sheetId="5" r:id="rId10"/>
-    <sheet name="t_billof_product" sheetId="7" r:id="rId11"/>
-    <sheet name="t_freight_order" sheetId="8" r:id="rId12"/>
-    <sheet name="t_payment" sheetId="9" r:id="rId13"/>
-    <sheet name="t_acct_policy" sheetId="10" r:id="rId14"/>
-    <sheet name="t_accts" sheetId="11" r:id="rId15"/>
-    <sheet name="t_coa" sheetId="12" r:id="rId16"/>
+    <sheet name="t_campaign" sheetId="18" r:id="rId6"/>
+    <sheet name="t_product" sheetId="4" r:id="rId7"/>
+    <sheet name="t_company_product" sheetId="13" r:id="rId8"/>
+    <sheet name="t_warehouse" sheetId="6" r:id="rId9"/>
+    <sheet name="t_company_warehouse" sheetId="16" r:id="rId10"/>
+    <sheet name="t_order" sheetId="5" r:id="rId11"/>
+    <sheet name="t_billof_product" sheetId="7" r:id="rId12"/>
+    <sheet name="t_inventory" sheetId="17" r:id="rId13"/>
+    <sheet name="t_freight_order" sheetId="8" r:id="rId14"/>
+    <sheet name="t_payment" sheetId="9" r:id="rId15"/>
+    <sheet name="t_acct_policy" sheetId="10" r:id="rId16"/>
+    <sheet name="t_accts" sheetId="11" r:id="rId17"/>
+    <sheet name="t_coa" sheetId="12" r:id="rId18"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2327" uniqueCount="1633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="1659">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5477,6 +5479,109 @@
   </si>
   <si>
     <t>订单甲方/买方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>product_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>price</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>quantity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>campaign_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>七夕情人节</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>begtime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>endtime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>立秋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中秋节</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>国庆节</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7-8月</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8月</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11月</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10月</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>双11购物狂欢节</t>
+  </si>
+  <si>
+    <t>12月</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>双12购物狂欢节</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>圣诞节</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"description":"双11购物狂欢节，这个可不用多说了吧！一年一度的购物盛宴，商家们可以大干一场，因为每年双11，消费能力都会达到巅峰，别错过！"}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"description":"双12购物狂欢节，双11之后的第二波购物狂潮。通常商家会以“消费者没抢到双11促销”为理由再次放送福利，尽管折扣力度和双11相比较小，但也有不少机会"}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"description":"一年末尾的浓浓冬意，亲朋好友都热衷于在圣诞节互赠礼物。所以，如果你有冬季商品要卖，这个节日促销时机绝对不能错过。冬天的商品在这个节日中格外受欢迎"}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"description":"国庆节，不同于其他国家，中国的国庆节在10月1日，而且还有七天的假期。这意味着我们的促销活动可以进行整整7天！无论你卖什么商品，都可以与国庆长假相结合，把生意做得火热"}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"description":"中秋节，吃月饼的好时机，同时也是购物的好时候。购物满xxx就送你美味的月饼，简直不能更甜"}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"description":"立秋，虽然不是正式节日，但它标志着秋天的来临。商家们开始推出‘秋天第一杯奶茶’，还有‘秋天第一支口红’或‘秋天第一件时尚衣物’，多种选择等你来抢购"}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"description":"七夕情人节，这可是个大日子！男女生的消费品都会打折促销，年轻人赶紧抓住机会送礼物给心上人，感情加分不停哦"}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">campaign_month </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -8744,14 +8849,14 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0809A7B5-F949-4F94-AB4A-C8F63E209D36}">
-  <dimension ref="A1:F2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38A6DE5-6BE8-42D9-8E17-5C5230227197}">
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="81.875" customWidth="1"/>
+    <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
@@ -8761,13 +8866,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1576</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1577</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E1" t="s">
         <v>5</v>
@@ -8780,19 +8885,239 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1613</v>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
         <v>45296.99722222222</v>
       </c>
     </row>
@@ -8803,6 +9128,72 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0809A7B5-F949-4F94-AB4A-C8F63E209D36}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="81.875" customWidth="1"/>
+    <col min="6" max="6" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A491D504-AE09-4D14-BD7B-F95BC5DE2CC2}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -8969,7 +9360,104 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EFBFA22-BDD8-4CD7-AF3F-D271876E5956}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="12.875" customWidth="1"/>
+    <col min="7" max="7" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2">
+        <v>1000</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="F3">
+        <v>1000</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F73FA18-B987-444A-B339-09CE35D7E8C2}">
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -9076,7 +9564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B9F82DD-9D92-4BA2-A7FE-9114B3F1FED4}">
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -9183,7 +9671,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D2F96A-1206-4BE2-BA64-3DDEC9C031F1}">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -9596,7 +10084,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACEF57BE-C827-48D2-B1B1-5408B794921D}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -9668,7 +10156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82ED0C5-D470-4836-91EC-2CC0CA9F9A1C}">
   <dimension ref="A1:F164"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -20427,6 +20915,258 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C5A3462-A51B-4305-8E8A-365D7E09AB66}">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1639</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F2" s="1">
+        <v>45607.99722222222</v>
+      </c>
+      <c r="G2" s="1">
+        <v>45608.99722222222</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1643</v>
+      </c>
+      <c r="F3" s="1">
+        <v>45607.99722222222</v>
+      </c>
+      <c r="G3" s="1">
+        <v>45608.99722222222</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F4" s="1">
+        <v>45607.99722222222</v>
+      </c>
+      <c r="G4" s="1">
+        <v>45608.99722222222</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F5" s="1">
+        <v>45607.99722222222</v>
+      </c>
+      <c r="G5" s="1">
+        <v>45608.99722222222</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1651</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F6" s="1">
+        <v>45607.99722222222</v>
+      </c>
+      <c r="G6" s="1">
+        <v>45608.99722222222</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F7" s="1">
+        <v>45607.99722222222</v>
+      </c>
+      <c r="G7" s="1">
+        <v>45608.99722222222</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F8" s="1">
+        <v>45607.99722222222</v>
+      </c>
+      <c r="G8" s="1">
+        <v>45608.99722222222</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DF16463-48C8-4AAF-8670-417CA0ABD58B}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -20672,7 +21412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C137C6B-005E-4E03-BEB3-517ADFC21587}">
   <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -21510,7 +22250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{516166F9-8240-4967-89E6-E801C1B6AF8A}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -21590,283 +22330,4 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38A6DE5-6BE8-42D9-8E17-5C5230227197}">
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1572</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1">
-        <v>45296.99722222222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1580</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1">
-        <v>45296.99722222222</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1575</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1">
-        <v>45296.99722222222</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1578</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>45296.99722222222</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1574</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>45296.99722222222</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1579</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>45296.99722222222</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1583</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>45296.99722222222</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1582</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1">
-        <v>45296.99722222222</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1584</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>4</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <v>45296.99722222222</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1618</v>
-      </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1">
-        <v>45296.99722222222</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1617</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>4</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1">
-        <v>45296.99722222222</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1619</v>
-      </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13">
-        <v>5</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1">
-        <v>45296.99722222222</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\jdbc\finance\acct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3003B0-B8C9-4FCF-BC6B-6B4EFB41EA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B507BCDB-1E4C-42A6-91C7-B9303858456D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="2" activeTab="5" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="10" activeTab="12" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
   </bookViews>
   <sheets>
     <sheet name="t_user" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="t_company_warehouse" sheetId="16" r:id="rId10"/>
     <sheet name="t_order" sheetId="5" r:id="rId11"/>
     <sheet name="t_billof_product" sheetId="7" r:id="rId12"/>
-    <sheet name="t_inventory" sheetId="17" r:id="rId13"/>
+    <sheet name="t_inventory_order" sheetId="17" r:id="rId13"/>
     <sheet name="t_freight_order" sheetId="8" r:id="rId14"/>
     <sheet name="t_payment" sheetId="9" r:id="rId15"/>
     <sheet name="t_acct_policy" sheetId="10" r:id="rId16"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="1659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2370" uniqueCount="1662">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5582,6 +5582,18 @@
   </si>
   <si>
     <t xml:space="preserve">campaign_month </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>batch_no</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>version</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>balance_qty</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -9362,44 +9374,62 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EFBFA22-BDD8-4CD7-AF3F-D271876E5956}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="12.875" customWidth="1"/>
-    <col min="7" max="7" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
         <v>1636</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1633</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1634</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>1635</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1661</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -9410,44 +9440,144 @@
         <v>1</v>
       </c>
       <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>11</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>100</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>1000</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2">
+        <v>1000</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1">
         <v>45296.99722222222</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
         <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>12</v>
       </c>
-      <c r="E3">
-        <v>30</v>
-      </c>
       <c r="F3">
+        <v>90</v>
+      </c>
+      <c r="G3">
         <v>1000</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3">
+        <v>1000</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>13</v>
+      </c>
+      <c r="F4">
+        <v>80</v>
+      </c>
+      <c r="G4">
+        <v>1000</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1000</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1">
+        <v>45296.99722222222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>-1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>950</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
         <v>45296.99722222222</v>
       </c>
     </row>

--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\jdbc\finance\acct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B507BCDB-1E4C-42A6-91C7-B9303858456D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285108D4-9D89-4592-8448-64A5C9C61B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="10" activeTab="12" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="9" activeTab="12" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
   </bookViews>
   <sheets>
     <sheet name="t_user" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="t_company_warehouse" sheetId="16" r:id="rId10"/>
     <sheet name="t_order" sheetId="5" r:id="rId11"/>
     <sheet name="t_billof_product" sheetId="7" r:id="rId12"/>
-    <sheet name="t_inventory_order" sheetId="17" r:id="rId13"/>
+    <sheet name="t_billof_inventory" sheetId="17" r:id="rId13"/>
     <sheet name="t_freight_order" sheetId="8" r:id="rId14"/>
     <sheet name="t_payment" sheetId="9" r:id="rId15"/>
     <sheet name="t_acct_policy" sheetId="10" r:id="rId16"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2370" uniqueCount="1662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2403" uniqueCount="1672">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5594,6 +5594,45 @@
   </si>
   <si>
     <t>balance_qty</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>import</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>营销活动初始导入</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取消订单退回库存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建订单移除库存</t>
+  </si>
+  <si>
+    <t>创建订单移除库存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATCH20240105000001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATCHYYYYMMDD000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATCH20240101000001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATCH20240105000002</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5684,7 +5723,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5704,6 +5743,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -9374,216 +9416,547 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EFBFA22-BDD8-4CD7-AF3F-D271876E5956}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>1636</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>1633</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>1634</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>1635</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>1659</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>1661</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>1660</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O1" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="9">
+        <v>99999999999.990005</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>45296.99722222222</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>11</v>
-      </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-      <c r="G2">
-        <v>1000</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1000</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1">
-        <v>45296.99722222222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
+      <c r="B3" t="s">
+        <v>1662</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3" s="9">
         <v>1000</v>
       </c>
-      <c r="H3">
+      <c r="J3" t="s">
+        <v>1670</v>
+      </c>
+      <c r="K3">
+        <v>1000</v>
+      </c>
+      <c r="L3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>1000</v>
-      </c>
-      <c r="J3">
+      <c r="M3">
         <v>1</v>
       </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3" s="1">
+      <c r="N3" s="1">
         <v>45296.99722222222</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O3" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1662</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="G4">
+        <v>12</v>
+      </c>
+      <c r="H4">
+        <v>90</v>
+      </c>
+      <c r="I4" s="9">
         <v>1000</v>
       </c>
-      <c r="H4">
+      <c r="J4" t="s">
+        <v>1670</v>
+      </c>
+      <c r="K4">
+        <v>1000</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
-      <c r="I4">
-        <v>1000</v>
-      </c>
-      <c r="J4">
+      <c r="M4">
         <v>1</v>
       </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1">
+      <c r="N4" s="1">
         <v>45296.99722222222</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O4" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>-1</v>
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1662</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>80</v>
+      </c>
+      <c r="I5" s="9">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1670</v>
+      </c>
+      <c r="K5">
+        <v>1000</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
+        <v>45296.99722222222</v>
+      </c>
+      <c r="O5" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>70</v>
+      </c>
+      <c r="I6" s="9">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1670</v>
+      </c>
+      <c r="K6">
+        <v>1000</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1">
+        <v>45296.99722222222</v>
+      </c>
+      <c r="O6" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>-1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
         <v>11</v>
       </c>
-      <c r="F5">
+      <c r="H7">
         <v>100</v>
       </c>
-      <c r="G5">
-        <v>50</v>
-      </c>
-      <c r="H5">
+      <c r="I7" s="9">
         <v>1</v>
       </c>
-      <c r="I5">
-        <v>950</v>
-      </c>
-      <c r="J5">
+      <c r="J7" t="s">
+        <v>1668</v>
+      </c>
+      <c r="K7">
+        <v>999</v>
+      </c>
+      <c r="L7">
         <v>2</v>
       </c>
-      <c r="K5">
+      <c r="M7">
         <v>1</v>
       </c>
-      <c r="L5" s="1">
+      <c r="N7" s="1">
         <v>45296.99722222222</v>
+      </c>
+      <c r="O7" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>-1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>12</v>
+      </c>
+      <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8" s="9">
+        <v>2</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1668</v>
+      </c>
+      <c r="K8">
+        <v>998</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1">
+        <v>45296.99722222222</v>
+      </c>
+      <c r="O8" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>-1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1668</v>
+      </c>
+      <c r="K9">
+        <v>996.5</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1">
+        <v>45296.99722222222</v>
+      </c>
+      <c r="O9" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>-1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>14</v>
+      </c>
+      <c r="H10">
+        <v>70</v>
+      </c>
+      <c r="I10" s="9">
+        <v>4</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1668</v>
+      </c>
+      <c r="K10">
+        <v>996</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1">
+        <v>45296.99722222222</v>
+      </c>
+      <c r="O10" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>14</v>
+      </c>
+      <c r="H11">
+        <v>70</v>
+      </c>
+      <c r="I11" s="9">
+        <v>4</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1671</v>
+      </c>
+      <c r="K11">
+        <v>1000</v>
+      </c>
+      <c r="L11">
+        <v>3</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
+        <v>45296.99722222222</v>
+      </c>
+      <c r="O11" t="s">
+        <v>1665</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\jdbc\finance\acct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285108D4-9D89-4592-8448-64A5C9C61B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F441A25-616B-481E-89A5-5D56654303B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="9" activeTab="12" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="11" activeTab="15" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
   </bookViews>
   <sheets>
     <sheet name="t_user" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2403" uniqueCount="1672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2421" uniqueCount="1675">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5633,6 +5633,18 @@
   </si>
   <si>
     <t>BATCH20240105000002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>policy0002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>应交税费</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BL</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -10176,7 +10188,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D2F96A-1206-4BE2-BA64-3DDEC9C031F1}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
@@ -10577,6 +10589,75 @@
       </c>
       <c r="G17" t="s">
         <v>1629</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1631</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct2_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\jdbc\finance\acct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F441A25-616B-481E-89A5-5D56654303B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236A6229-0778-456D-A67A-85145C551FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="11" activeTab="15" xr2:uid="{9F52F4E2-D186-4BF8-BDC0-8A6A204FCC8B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2421" uniqueCount="1675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="1675">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -10188,7 +10188,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D2F96A-1206-4BE2-BA64-3DDEC9C031F1}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
@@ -10658,6 +10658,52 @@
       </c>
       <c r="G20" t="s">
         <v>1631</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1625</v>
       </c>
     </row>
   </sheetData>
